--- a/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_39.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.1/Output_39_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3051710.402538622</v>
+        <v>3052199.571677396</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23349182.4754368</v>
+        <v>23349182.47543681</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23349182.4754368</v>
+        <v>23349182.47543681</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14944382.20375631</v>
+        <v>14944382.20375632</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14944382.20375631</v>
+        <v>14944382.20375632</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557428</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299369</v>
@@ -666,7 +666,7 @@
         <v>4.36328960686842</v>
       </c>
       <c r="F2" t="n">
-        <v>114.5107965447948</v>
+        <v>4.889628708011628</v>
       </c>
       <c r="G2" t="n">
         <v>2.21365369405116</v>
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>90.56694862740821</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>43.03425476022782</v>
+        <v>43.0342547602285</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -705,25 +705,25 @@
         <v>153.9079857629678</v>
       </c>
       <c r="S2" t="n">
-        <v>59.67068036513674</v>
+        <v>59.67068036513673</v>
       </c>
       <c r="T2" t="n">
-        <v>179.9179535878602</v>
+        <v>179.9179535878601</v>
       </c>
       <c r="U2" t="n">
-        <v>8.171524367403851</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>15.04289519321478</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606675</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>111.3174326828062</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>223.0000000000002</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>188.6886500422919</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000002</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>51.22211317215825</v>
       </c>
       <c r="T3" t="n">
-        <v>2.028557670343778</v>
+        <v>2.028557670343777</v>
       </c>
       <c r="U3" t="n">
-        <v>223.0000000000003</v>
+        <v>0.1560201375450109</v>
       </c>
       <c r="V3" t="n">
-        <v>223.0000000000003</v>
+        <v>14.51066719151993</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982829</v>
       </c>
       <c r="X3" t="n">
-        <v>162.016699419831</v>
+        <v>130.4392488763141</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -894,19 +894,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299369</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.36328960686842</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>11.57553955092101</v>
       </c>
       <c r="G5" t="n">
-        <v>2.21365369405116</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>43.03425476022726</v>
+        <v>43.03425476022782</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -939,22 +939,22 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>153.9079857629678</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.922912845283108</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>223.0000000000004</v>
+        <v>7.815173375583139</v>
       </c>
       <c r="V5" t="n">
-        <v>223.0000000000004</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="W5" t="n">
-        <v>223.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606675</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>46.95796825592343</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>223.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>218.5556286162623</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="I6" t="n">
-        <v>186.3521041922195</v>
+        <v>188.6886500422919</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,25 +1018,25 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>95.99168408483186</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>51.22211317215825</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.028557670343777</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1560201375450109</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719151993</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="X6" t="n">
-        <v>223.0000000000004</v>
+        <v>19.86273944538732</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>12.08551304189393</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>13.41551434100881</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33000129911484</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
@@ -1146,7 +1146,7 @@
         <v>2.213653694051387</v>
       </c>
       <c r="H8" t="n">
-        <v>73.67573361433254</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>90.56694862740821</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>43.03425476022748</v>
+        <v>43.0342547602276</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1179,10 +1179,10 @@
         <v>153.9079857629678</v>
       </c>
       <c r="S8" t="n">
-        <v>59.67068036513697</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="U8" t="n">
         <v>223.0000000000004</v>
@@ -1191,13 +1191,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>163.4768936006939</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>223.0000000000004</v>
+        <v>221.1411295819855</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>188.6886500422919</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>67.64590659991353</v>
+        <v>67.6459065999135</v>
       </c>
       <c r="R9" t="n">
-        <v>95.99168408483212</v>
+        <v>95.99168408483209</v>
       </c>
       <c r="S9" t="n">
-        <v>51.22211317215848</v>
+        <v>51.22211317215847</v>
       </c>
       <c r="T9" t="n">
-        <v>2.028557670344005</v>
+        <v>2.028557670344004</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1560201375452383</v>
+        <v>0.1560201375452382</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>1.033671519411161</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>135.627568788472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.41551434100876</v>
+        <v>13.41551434100878</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1371,19 +1371,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>165.7517773277447</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>178.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>178.8896287080119</v>
+        <v>-1.165575986972508e-12</v>
       </c>
       <c r="G11" t="n">
-        <v>176.2136536940514</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>166.2000506633264</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1398,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>43.03425476022704</v>
       </c>
       <c r="N11" t="n">
-        <v>43.03425476022681</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1419,19 +1419,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>196.4184000000032</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>69.23382219211439</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>176.028557670344</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>174.1560201375452</v>
       </c>
       <c r="V12" t="n">
-        <v>37.01669941983154</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>206.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>223.0000000000004</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>203.6862452324947</v>
-      </c>
-      <c r="O13" t="n">
-        <v>223.0000000000004</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
         <v>223.0000000000004</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>178.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>64.84145669908182</v>
+        <v>178.8896287080119</v>
       </c>
       <c r="G14" t="n">
         <v>176.2136536940514</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>64.31511759793902</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1635,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>43.03425476022636</v>
       </c>
       <c r="N14" t="n">
-        <v>43.03425476022726</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1684,10 +1684,10 @@
         <v>158.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>133.6772655457881</v>
       </c>
       <c r="D15" t="n">
-        <v>35.48623496313881</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>98.19103058264754</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1763,19 +1763,19 @@
         <v>61.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>46.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>49.85268692590768</v>
       </c>
       <c r="E16" t="n">
-        <v>18.15480439466783</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>48.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>18.35141382513659</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>94.59785766597588</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>186.0855130418942</v>
@@ -1826,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>21.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>61.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -1839,25 +1839,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="D17" t="n">
-        <v>118.9654310217957</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>178.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>178.8896287080119</v>
+        <v>-1.503225895005708e-12</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>166.2000506633264</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1872,10 +1872,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>43.03425476022704</v>
       </c>
       <c r="N17" t="n">
-        <v>43.03425476022591</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1893,13 +1893,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>196.4184000000036</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>158.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>135.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>98.19103058264754</v>
+        <v>-2.250999386887997e-12</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="T18" t="n">
         <v>176.028557670344</v>
       </c>
       <c r="U18" t="n">
-        <v>39.23615985610679</v>
+        <v>113.9705462379463</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>61.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>46.72524664804467</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>59.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>54.98090483695654</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>48.38285596774193</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2027,13 +2027,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>17.60073219060056</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>186.0855130418942</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>223.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>94.48186653765541</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>61.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>196.4184000000042</v>
+        <v>223.0000000000005</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2085,13 +2085,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>178.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>64.84145669908207</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.431763142097006e-12</v>
+        <v>176.2136536940514</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2109,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.363794715972034</v>
+        <v>43.03425476022636</v>
       </c>
       <c r="N20" t="n">
-        <v>38.670460044255</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2136,10 +2136,10 @@
         <v>223.0000000000005</v>
       </c>
       <c r="V20" t="n">
-        <v>223.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>223.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>158.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>135.0999124455193</v>
+        <v>133.6772655457868</v>
       </c>
       <c r="D21" t="n">
-        <v>121.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>116.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2212,13 +2212,13 @@
         <v>176.028557670344</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>174.1560201375452</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>92.68014576452399</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2246,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>48.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>18.35141382513659</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>94.59785766597588</v>
+        <v>17.60073219060056</v>
       </c>
       <c r="M22" t="n">
-        <v>141.048310201933</v>
+        <v>186.0855130418942</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>223.0000000000005</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>124.3058075717079</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.628725588449706e-12</v>
+        <v>-2.178525711072106e-12</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2346,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>43.03425476022625</v>
       </c>
       <c r="N23" t="n">
-        <v>43.03425476022569</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2398,16 +2398,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>62.69011000373501</v>
       </c>
       <c r="E24" t="n">
-        <v>65.32935918938553</v>
+        <v>116.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>113.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>98.9135736108764</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>188.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>173.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2477,13 +2477,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>59.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>54.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>43.52616353090291</v>
+        <v>33.73747885170702</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>124.3058075717079</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2550,22 +2550,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>189</v>
       </c>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>166.471200000002</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2629,22 +2629,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>74.20348673661283</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>143.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>135.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>120.9135736108764</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2686,13 +2686,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>82.35321524139458</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>30.06364696071072</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4.733578957086475</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2787,76 +2787,76 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>166.4712000000024</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.053026017628108e-12</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>57.19865025538263</v>
+      </c>
+      <c r="N29" t="n">
+        <v>44.35396365345164</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>189.0000000000001</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
         <v>189.0000000000001</v>
       </c>
-      <c r="E29" t="n">
-        <v>166.5815712919902</v>
-      </c>
-      <c r="F29" t="n">
-        <v>188.8896287080119</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-6.028261402505088e-13</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>101.5526139088338</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>189.0000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.37128755448305</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>145.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.238049662788398e-12</v>
+        <v>123.6439270794769</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>123.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>108.1910305826475</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>189.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>104.5978576659759</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>189.0000000000001</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>152.039751905019</v>
       </c>
       <c r="S31" t="n">
-        <v>47.44189423904313</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3027,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>166.4712000000029</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.531363387341808e-12</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.165575986972508e-12</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>101.5526139088342</v>
+        <v>101.5526139088339</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3078,22 +3078,22 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
         <v>189.0000000000003</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>189.0000000000003</v>
       </c>
       <c r="W32" t="n">
         <v>189.0000000000003</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>166.4712000000029</v>
       </c>
       <c r="Y32" t="n">
-        <v>189.0000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>120.6080721954412</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3112,16 +3112,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>126.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-1.800799509510398e-12</v>
       </c>
       <c r="H33" t="n">
-        <v>108.1910305826475</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>189.0000000000003</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>189.0000000000003</v>
@@ -3163,13 +3163,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>189.0000000000003</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>189.0000000000003</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>166.4712000000029</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>152.039751905019</v>
       </c>
       <c r="Q34" t="n">
-        <v>152.039751905019</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>189.0000000000004</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-1.840875803038907e-12</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>57.19865025538263</v>
+        <v>101.5526139088338</v>
       </c>
       <c r="N35" t="n">
-        <v>44.35396365345029</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>189.0000000000004</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>166.4712000000035</v>
       </c>
       <c r="U35" t="n">
-        <v>166.4712000000014</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>189.0000000000004</v>
-      </c>
-      <c r="W35" t="n">
-        <v>189.0000000000004</v>
-      </c>
-      <c r="X35" t="n">
-        <v>189.0000000000004</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.917446973817992e-12</v>
+        <v>-2.363549356232397e-12</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3394,16 +3394,16 @@
         <v>189.0000000000004</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>186.028557670344</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>169.4426423296599</v>
       </c>
       <c r="V36" t="n">
-        <v>166.4712000000035</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>189.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>152.039751905019</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3461,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>189.0000000000004</v>
       </c>
       <c r="Q37" t="n">
-        <v>189.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>152.039751905019</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3510,13 +3510,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-6.028261402505088e-13</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-9.003997547551989e-13</v>
       </c>
       <c r="H38" t="n">
-        <v>-7.153761095949087e-13</v>
+        <v>-9.003997547551989e-13</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>166.4712000000037</v>
+        <v>166.4712000000041</v>
       </c>
       <c r="V38" t="n">
         <v>189.0000000000005</v>
@@ -3592,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.125499693443999e-12</v>
+        <v>-1.688249540165998e-12</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.012949724099599e-12</v>
+        <v>-9.566747394273988e-13</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3640,7 +3640,7 @@
         <v>189.0000000000005</v>
       </c>
       <c r="W39" t="n">
-        <v>166.4712000000036</v>
+        <v>166.471200000004</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3741,70 +3741,70 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
+        <v>166.4712000000036</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>101.5526139088318</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>189.0000000000005</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>101.5526139088314</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
         <v>189.0000000000005</v>
       </c>
-      <c r="T41" t="n">
-        <v>166.4712000000036</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
         <v>189.0000000000005</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>8.460579226453719</v>
       </c>
       <c r="S42" t="n">
         <v>189.0000000000005</v>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>8.460579226453691</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>189.0000000000005</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>189.0000000000005</v>
+        <v>166.4712000000036</v>
       </c>
       <c r="G44" t="n">
         <v>189.0000000000005</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>189.0000000000005</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>166.4712000000037</v>
+        <v>189.0000000000005</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>292.0505277332988</v>
+        <v>89.84030908260016</v>
       </c>
       <c r="C2" t="n">
-        <v>242.0762062757294</v>
+        <v>39.86598762503077</v>
       </c>
       <c r="D2" t="n">
-        <v>231.6326146193157</v>
+        <v>29.42239596861707</v>
       </c>
       <c r="E2" t="n">
-        <v>227.2252513800547</v>
+        <v>25.01503272935604</v>
       </c>
       <c r="F2" t="n">
-        <v>111.5577801226862</v>
+        <v>20.0760138323746</v>
       </c>
       <c r="G2" t="n">
-        <v>109.3217662903113</v>
+        <v>17.83999999999969</v>
       </c>
       <c r="H2" t="n">
-        <v>109.3217662903113</v>
+        <v>17.83999999999989</v>
       </c>
       <c r="I2" t="n">
         <v>17.83999999999998</v>
       </c>
       <c r="J2" t="n">
-        <v>112.8583978877123</v>
+        <v>112.8583978877124</v>
       </c>
       <c r="K2" t="n">
-        <v>307.2615239178631</v>
+        <v>307.2615239178632</v>
       </c>
       <c r="L2" t="n">
-        <v>528.0315239178634</v>
+        <v>528.0315239178635</v>
       </c>
       <c r="M2" t="n">
-        <v>528.0315239178634</v>
+        <v>528.0315239178635</v>
       </c>
       <c r="N2" t="n">
-        <v>484.5625797156131</v>
+        <v>484.5625797156125</v>
       </c>
       <c r="O2" t="n">
-        <v>672.5154127568595</v>
+        <v>672.5154127568591</v>
       </c>
       <c r="P2" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="Q2" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="R2" t="n">
-        <v>736.5373881182163</v>
+        <v>736.537388118216</v>
       </c>
       <c r="S2" t="n">
-        <v>676.2639736079772</v>
+        <v>676.2639736079768</v>
       </c>
       <c r="T2" t="n">
-        <v>494.528666953573</v>
+        <v>494.5286669535726</v>
       </c>
       <c r="U2" t="n">
-        <v>486.2746019359933</v>
+        <v>494.5286669535726</v>
       </c>
       <c r="V2" t="n">
-        <v>486.2746019359933</v>
+        <v>494.5286669535726</v>
       </c>
       <c r="W2" t="n">
-        <v>486.2746019359933</v>
+        <v>479.3338233240627</v>
       </c>
       <c r="X2" t="n">
-        <v>292.0505277332988</v>
+        <v>285.1097491213683</v>
       </c>
       <c r="Y2" t="n">
-        <v>292.0505277332988</v>
+        <v>172.6678979266146</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.8399999999981</v>
+        <v>433.6871212548405</v>
       </c>
       <c r="C3" t="n">
-        <v>17.8399999999981</v>
+        <v>433.6871212548405</v>
       </c>
       <c r="D3" t="n">
-        <v>17.8399999999981</v>
+        <v>433.6871212548405</v>
       </c>
       <c r="E3" t="n">
-        <v>17.83999999999997</v>
+        <v>208.434596002315</v>
       </c>
       <c r="F3" t="n">
-        <v>17.83999999999997</v>
+        <v>208.434596002315</v>
       </c>
       <c r="G3" t="n">
-        <v>17.83999999999997</v>
+        <v>208.434596002315</v>
       </c>
       <c r="H3" t="n">
-        <v>17.83999999999997</v>
+        <v>208.434596002315</v>
       </c>
       <c r="I3" t="n">
         <v>17.83999999999997</v>
@@ -4406,46 +4406,46 @@
         <v>247.3639098907707</v>
       </c>
       <c r="L3" t="n">
-        <v>312.0514076360537</v>
+        <v>312.0514076360538</v>
       </c>
       <c r="M3" t="n">
-        <v>395.7202695065359</v>
+        <v>395.7202695065354</v>
       </c>
       <c r="N3" t="n">
-        <v>616.4902695065362</v>
+        <v>616.4902695065356</v>
       </c>
       <c r="O3" t="n">
-        <v>671.2300000000018</v>
+        <v>671.2300000000014</v>
       </c>
       <c r="P3" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="Q3" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="R3" t="n">
-        <v>666.7474747474765</v>
+        <v>666.7474747474762</v>
       </c>
       <c r="S3" t="n">
-        <v>666.7474747474765</v>
+        <v>615.0079664927709</v>
       </c>
       <c r="T3" t="n">
-        <v>664.6984265956141</v>
+        <v>612.9589183409086</v>
       </c>
       <c r="U3" t="n">
-        <v>439.4459013430886</v>
+        <v>612.8013222423782</v>
       </c>
       <c r="V3" t="n">
-        <v>214.1933760905631</v>
+        <v>598.1440826549843</v>
       </c>
       <c r="W3" t="n">
-        <v>181.4932317372012</v>
+        <v>565.4439383016224</v>
       </c>
       <c r="X3" t="n">
-        <v>17.8399999999981</v>
+        <v>433.6871212548405</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.8399999999981</v>
+        <v>433.6871212548405</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="C4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="D4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="E4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="F4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="G4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="H4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="I4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="J4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="K4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="L4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="M4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="N4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="O4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="P4" t="n">
-        <v>892.000000000002</v>
+        <v>892.0000000000016</v>
       </c>
       <c r="Q4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="R4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="S4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="T4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="U4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="V4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="W4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="X4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
       <c r="Y4" t="n">
-        <v>878.4489754131245</v>
+        <v>878.448975413124</v>
       </c>
     </row>
     <row r="5">
@@ -4534,34 +4534,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.07601383237443</v>
+        <v>309.1666741422054</v>
       </c>
       <c r="C5" t="n">
-        <v>20.07601383237443</v>
+        <v>259.192352684636</v>
       </c>
       <c r="D5" t="n">
-        <v>20.07601383237443</v>
+        <v>259.192352684636</v>
       </c>
       <c r="E5" t="n">
-        <v>20.07601383237443</v>
+        <v>254.784989445375</v>
       </c>
       <c r="F5" t="n">
-        <v>20.07601383237443</v>
+        <v>243.0925252525255</v>
       </c>
       <c r="G5" t="n">
-        <v>17.83999999999952</v>
+        <v>17.83999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>17.83999999999952</v>
+        <v>17.83999999999998</v>
       </c>
       <c r="I5" t="n">
         <v>17.83999999999998</v>
       </c>
       <c r="J5" t="n">
-        <v>112.8583978877123</v>
+        <v>112.8583978877124</v>
       </c>
       <c r="K5" t="n">
-        <v>307.2615239178631</v>
+        <v>307.2615239178632</v>
       </c>
       <c r="L5" t="n">
         <v>528.0315239178633</v>
@@ -4570,40 +4570,40 @@
         <v>528.0315239178633</v>
       </c>
       <c r="N5" t="n">
-        <v>484.5625797156135</v>
+        <v>484.562579715613</v>
       </c>
       <c r="O5" t="n">
-        <v>672.51541275686</v>
+        <v>672.5154127568595</v>
       </c>
       <c r="P5" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="Q5" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="R5" t="n">
-        <v>892.0000000000025</v>
+        <v>736.5373881182164</v>
       </c>
       <c r="S5" t="n">
-        <v>892.0000000000025</v>
+        <v>736.5373881182164</v>
       </c>
       <c r="T5" t="n">
-        <v>890.0576637926458</v>
+        <v>736.5373881182164</v>
       </c>
       <c r="U5" t="n">
-        <v>664.8051385401202</v>
+        <v>728.6432735974254</v>
       </c>
       <c r="V5" t="n">
-        <v>439.5526132875946</v>
+        <v>503.3907483448999</v>
       </c>
       <c r="W5" t="n">
-        <v>214.3000880350689</v>
+        <v>503.3907483448999</v>
       </c>
       <c r="X5" t="n">
-        <v>20.07601383237443</v>
+        <v>309.1666741422054</v>
       </c>
       <c r="Y5" t="n">
-        <v>20.07601383237443</v>
+        <v>309.1666741422054</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>652.090235160083</v>
+        <v>481.11941242244</v>
       </c>
       <c r="C6" t="n">
-        <v>652.090235160083</v>
+        <v>481.11941242244</v>
       </c>
       <c r="D6" t="n">
-        <v>652.090235160083</v>
+        <v>433.6871212548406</v>
       </c>
       <c r="E6" t="n">
-        <v>652.090235160083</v>
+        <v>433.6871212548406</v>
       </c>
       <c r="F6" t="n">
-        <v>652.090235160083</v>
+        <v>433.6871212548406</v>
       </c>
       <c r="G6" t="n">
-        <v>426.8377099075574</v>
+        <v>433.6871212548406</v>
       </c>
       <c r="H6" t="n">
-        <v>206.0744486790096</v>
+        <v>208.434596002315</v>
       </c>
       <c r="I6" t="n">
         <v>17.83999999999997</v>
@@ -4640,49 +4640,49 @@
         <v>219.0514877224687</v>
       </c>
       <c r="K6" t="n">
-        <v>439.8214877224691</v>
+        <v>247.3639098907707</v>
       </c>
       <c r="L6" t="n">
-        <v>504.5089854677522</v>
+        <v>312.0514076360538</v>
       </c>
       <c r="M6" t="n">
-        <v>725.2789854677526</v>
+        <v>312.0514076360538</v>
       </c>
       <c r="N6" t="n">
-        <v>785.5447893818156</v>
+        <v>532.8214076360541</v>
       </c>
       <c r="O6" t="n">
-        <v>840.2845198752813</v>
+        <v>671.2300000000018</v>
       </c>
       <c r="P6" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="Q6" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="R6" t="n">
-        <v>892.0000000000025</v>
+        <v>795.0387029446163</v>
       </c>
       <c r="S6" t="n">
-        <v>892.0000000000025</v>
+        <v>743.299194689911</v>
       </c>
       <c r="T6" t="n">
-        <v>892.0000000000025</v>
+        <v>741.2501465380486</v>
       </c>
       <c r="U6" t="n">
-        <v>892.0000000000025</v>
+        <v>741.0925504395183</v>
       </c>
       <c r="V6" t="n">
-        <v>877.3427604126086</v>
+        <v>726.4353108521244</v>
       </c>
       <c r="W6" t="n">
-        <v>877.3427604126086</v>
+        <v>501.1827855995989</v>
       </c>
       <c r="X6" t="n">
-        <v>652.090235160083</v>
+        <v>481.11941242244</v>
       </c>
       <c r="Y6" t="n">
-        <v>652.090235160083</v>
+        <v>481.11941242244</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="C7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="D7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="E7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="F7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="G7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="H7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="I7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="J7" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="K7" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="L7" t="n">
-        <v>892.0000000000025</v>
+        <v>892.000000000002</v>
       </c>
       <c r="M7" t="n">
-        <v>879.7924110687965</v>
+        <v>892.000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>879.7924110687965</v>
+        <v>892.000000000002</v>
       </c>
       <c r="O7" t="n">
-        <v>879.7924110687965</v>
+        <v>892.000000000002</v>
       </c>
       <c r="P7" t="n">
-        <v>879.7924110687965</v>
+        <v>892.000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>879.7924110687965</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="R7" t="n">
-        <v>879.7924110687965</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="S7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="T7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="U7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="V7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="W7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="X7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
       <c r="Y7" t="n">
-        <v>878.4489754131249</v>
+        <v>878.4489754131245</v>
       </c>
     </row>
     <row r="8">
@@ -4771,34 +4771,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>255.7420083166832</v>
+        <v>120.9041622589294</v>
       </c>
       <c r="C8" t="n">
-        <v>205.7676868591136</v>
+        <v>120.9041622589294</v>
       </c>
       <c r="D8" t="n">
-        <v>195.3240952026996</v>
+        <v>120.9041622589294</v>
       </c>
       <c r="E8" t="n">
-        <v>190.9167319634384</v>
+        <v>116.4967990196681</v>
       </c>
       <c r="F8" t="n">
-        <v>185.9777130664567</v>
+        <v>111.5577801226864</v>
       </c>
       <c r="G8" t="n">
-        <v>183.7416992340816</v>
+        <v>109.3217662903113</v>
       </c>
       <c r="H8" t="n">
         <v>109.3217662903113</v>
       </c>
       <c r="I8" t="n">
-        <v>17.83999999999997</v>
+        <v>17.83999999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>112.8583978877123</v>
+        <v>112.8583978877124</v>
       </c>
       <c r="K8" t="n">
-        <v>307.2615239178631</v>
+        <v>307.2615239178632</v>
       </c>
       <c r="L8" t="n">
         <v>528.0315239178635</v>
@@ -4807,7 +4807,7 @@
         <v>528.0315239178635</v>
       </c>
       <c r="N8" t="n">
-        <v>484.5625797156135</v>
+        <v>484.5625797156134</v>
       </c>
       <c r="O8" t="n">
         <v>672.51541275686</v>
@@ -4819,28 +4819,28 @@
         <v>892.0000000000025</v>
       </c>
       <c r="R8" t="n">
-        <v>736.5373881182168</v>
+        <v>736.5373881182169</v>
       </c>
       <c r="S8" t="n">
-        <v>676.2639736079774</v>
+        <v>736.5373881182169</v>
       </c>
       <c r="T8" t="n">
-        <v>676.2639736079774</v>
+        <v>511.2848628656913</v>
       </c>
       <c r="U8" t="n">
-        <v>451.0114483554518</v>
+        <v>286.0323376131656</v>
       </c>
       <c r="V8" t="n">
-        <v>451.0114483554518</v>
+        <v>286.0323376131656</v>
       </c>
       <c r="W8" t="n">
-        <v>451.0114483554518</v>
+        <v>120.9041622589294</v>
       </c>
       <c r="X8" t="n">
-        <v>451.0114483554518</v>
+        <v>120.9041622589294</v>
       </c>
       <c r="Y8" t="n">
-        <v>338.5695971606978</v>
+        <v>120.9041622589294</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>468.3450505050513</v>
+        <v>657.0619996204827</v>
       </c>
       <c r="C9" t="n">
-        <v>468.3450505050513</v>
+        <v>657.0619996204827</v>
       </c>
       <c r="D9" t="n">
-        <v>243.0925252525256</v>
+        <v>431.809474367957</v>
       </c>
       <c r="E9" t="n">
-        <v>243.0925252525256</v>
+        <v>431.809474367957</v>
       </c>
       <c r="F9" t="n">
-        <v>243.0925252525256</v>
+        <v>431.809474367957</v>
       </c>
       <c r="G9" t="n">
-        <v>243.0925252525256</v>
+        <v>431.809474367957</v>
       </c>
       <c r="H9" t="n">
-        <v>17.83999999999997</v>
+        <v>208.434596002315</v>
       </c>
       <c r="I9" t="n">
         <v>17.83999999999997</v>
@@ -4877,19 +4877,19 @@
         <v>219.0514877224687</v>
       </c>
       <c r="K9" t="n">
-        <v>279.3172916365318</v>
+        <v>439.8214877224691</v>
       </c>
       <c r="L9" t="n">
-        <v>344.0047893818149</v>
+        <v>504.5089854677522</v>
       </c>
       <c r="M9" t="n">
-        <v>564.7747893818153</v>
+        <v>504.5089854677522</v>
       </c>
       <c r="N9" t="n">
-        <v>785.5447893818156</v>
+        <v>616.4902695065363</v>
       </c>
       <c r="O9" t="n">
-        <v>840.2845198752813</v>
+        <v>671.2300000000021</v>
       </c>
       <c r="P9" t="n">
         <v>892.0000000000025</v>
@@ -4898,28 +4898,28 @@
         <v>823.6708014142313</v>
       </c>
       <c r="R9" t="n">
-        <v>726.7095043588453</v>
+        <v>726.7095043588454</v>
       </c>
       <c r="S9" t="n">
-        <v>674.9699961041397</v>
+        <v>674.9699961041398</v>
       </c>
       <c r="T9" t="n">
-        <v>672.9209479522771</v>
+        <v>672.9209479522772</v>
       </c>
       <c r="U9" t="n">
-        <v>672.7633518537465</v>
+        <v>672.7633518537466</v>
       </c>
       <c r="V9" t="n">
-        <v>658.1061122663524</v>
+        <v>658.1061122663525</v>
       </c>
       <c r="W9" t="n">
-        <v>625.4059679129903</v>
+        <v>657.0619996204827</v>
       </c>
       <c r="X9" t="n">
-        <v>605.3425947358311</v>
+        <v>657.0619996204827</v>
       </c>
       <c r="Y9" t="n">
-        <v>468.3450505050513</v>
+        <v>657.0619996204827</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="C10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="D10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="E10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="F10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="G10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="H10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="I10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="J10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="K10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="L10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="M10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="N10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="O10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="P10" t="n">
-        <v>31.39102458687564</v>
+        <v>31.39102458687611</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="R10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="S10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="T10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="U10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="V10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="W10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="X10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999855</v>
       </c>
     </row>
     <row r="11">
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>892.0000000000025</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="C11" t="n">
-        <v>892.0000000000025</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="D11" t="n">
-        <v>724.5739622952099</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="E11" t="n">
-        <v>544.4090232983729</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="F11" t="n">
-        <v>363.7124286438154</v>
+        <v>17.83999999999958</v>
       </c>
       <c r="G11" t="n">
-        <v>185.7188390538645</v>
+        <v>17.83999999999958</v>
       </c>
       <c r="H11" t="n">
-        <v>17.83999999999946</v>
+        <v>17.83999999999958</v>
       </c>
       <c r="I11" t="n">
-        <v>17.83999999999946</v>
+        <v>17.83999999999958</v>
       </c>
       <c r="J11" t="n">
-        <v>112.8583978877118</v>
+        <v>112.8583978877119</v>
       </c>
       <c r="K11" t="n">
-        <v>307.2615239178626</v>
+        <v>307.2615239178627</v>
       </c>
       <c r="L11" t="n">
-        <v>528.0315239178628</v>
+        <v>528.0315239178631</v>
       </c>
       <c r="M11" t="n">
-        <v>528.0315239178628</v>
+        <v>484.5625797156135</v>
       </c>
       <c r="N11" t="n">
         <v>484.5625797156135</v>
@@ -5062,22 +5062,22 @@
         <v>892.0000000000025</v>
       </c>
       <c r="T11" t="n">
-        <v>892.0000000000025</v>
+        <v>666.7474747474769</v>
       </c>
       <c r="U11" t="n">
-        <v>892.0000000000025</v>
+        <v>666.7474747474769</v>
       </c>
       <c r="V11" t="n">
-        <v>892.0000000000025</v>
+        <v>441.4949494949512</v>
       </c>
       <c r="W11" t="n">
-        <v>892.0000000000025</v>
+        <v>216.2424242424256</v>
       </c>
       <c r="X11" t="n">
-        <v>892.0000000000025</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="Y11" t="n">
-        <v>892.0000000000025</v>
+        <v>17.8399999999981</v>
       </c>
     </row>
     <row r="12">
@@ -5087,46 +5087,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="C12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="D12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="E12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="F12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="G12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="H12" t="n">
-        <v>17.83999999999764</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="I12" t="n">
-        <v>54.77823645812864</v>
+        <v>54.77823645812909</v>
       </c>
       <c r="J12" t="n">
-        <v>254.5396296720869</v>
+        <v>61.70946875571182</v>
       </c>
       <c r="K12" t="n">
-        <v>282.8520518403888</v>
+        <v>90.02189092401375</v>
       </c>
       <c r="L12" t="n">
-        <v>354.5609271883226</v>
+        <v>310.7918909240141</v>
       </c>
       <c r="M12" t="n">
-        <v>404.5907967053755</v>
+        <v>310.7918909240141</v>
       </c>
       <c r="N12" t="n">
-        <v>493.7274680925523</v>
+        <v>310.7918909240141</v>
       </c>
       <c r="O12" t="n">
-        <v>700.6164107992937</v>
+        <v>531.5618909240145</v>
       </c>
       <c r="P12" t="n">
         <v>752.3318909240149</v>
@@ -5144,19 +5144,19 @@
         <v>263.6883255855129</v>
       </c>
       <c r="U12" t="n">
-        <v>263.6883255855129</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="V12" t="n">
-        <v>226.2977201109356</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="W12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="X12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.83999999999764</v>
+        <v>87.77315372940657</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="C13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="D13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="E13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="F13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="G13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="H13" t="n">
-        <v>140.8263685309573</v>
+        <v>140.8263685309577</v>
       </c>
       <c r="I13" t="n">
-        <v>210.3151373031058</v>
+        <v>210.3151373031062</v>
       </c>
       <c r="J13" t="n">
-        <v>431.0851373031061</v>
+        <v>431.0851373031066</v>
       </c>
       <c r="K13" t="n">
-        <v>448.8362073055483</v>
+        <v>448.8362073055487</v>
       </c>
       <c r="L13" t="n">
-        <v>448.8362073055483</v>
+        <v>448.8362073055487</v>
       </c>
       <c r="M13" t="n">
-        <v>448.8362073055483</v>
+        <v>448.8362073055487</v>
       </c>
       <c r="N13" t="n">
-        <v>243.0925252525233</v>
+        <v>223.5836820530231</v>
       </c>
       <c r="O13" t="n">
-        <v>17.83999999999764</v>
+        <v>223.5836820530231</v>
       </c>
       <c r="P13" t="n">
-        <v>17.83999999999764</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="Q13" t="n">
-        <v>17.83999999999764</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="R13" t="n">
-        <v>17.83999999999764</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="S13" t="n">
-        <v>17.83999999999764</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="T13" t="n">
-        <v>36.58478079814677</v>
+        <v>36.58478079814722</v>
       </c>
       <c r="U13" t="n">
-        <v>110.9133662233186</v>
+        <v>110.9133662233191</v>
       </c>
       <c r="V13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="W13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="X13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
       <c r="Y13" t="n">
-        <v>137.4747591092646</v>
+        <v>137.4747591092651</v>
       </c>
     </row>
     <row r="14">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>441.4949494949512</v>
+        <v>666.7474747474769</v>
       </c>
       <c r="C14" t="n">
         <v>441.4949494949512</v>
@@ -5254,31 +5254,31 @@
         <v>441.4949494949512</v>
       </c>
       <c r="E14" t="n">
-        <v>261.3300104981142</v>
+        <v>441.4949494949512</v>
       </c>
       <c r="F14" t="n">
-        <v>195.8335895899508</v>
+        <v>260.7983548403938</v>
       </c>
       <c r="G14" t="n">
-        <v>17.83999999999989</v>
+        <v>82.80476525044293</v>
       </c>
       <c r="H14" t="n">
-        <v>17.83999999999989</v>
+        <v>17.83999999999946</v>
       </c>
       <c r="I14" t="n">
-        <v>17.83999999999935</v>
+        <v>17.83999999999878</v>
       </c>
       <c r="J14" t="n">
-        <v>112.8583978877117</v>
+        <v>112.8583978877111</v>
       </c>
       <c r="K14" t="n">
-        <v>307.2615239178624</v>
+        <v>307.2615239178618</v>
       </c>
       <c r="L14" t="n">
-        <v>528.0315239178633</v>
+        <v>528.0315239178624</v>
       </c>
       <c r="M14" t="n">
-        <v>528.0315239178633</v>
+        <v>484.5625797156135</v>
       </c>
       <c r="N14" t="n">
         <v>484.5625797156135</v>
@@ -5327,40 +5327,40 @@
         <v>152.8675409553396</v>
       </c>
       <c r="C15" t="n">
-        <v>152.8675409553396</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="D15" t="n">
-        <v>117.0228591743913</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="E15" t="n">
-        <v>117.0228591743913</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="F15" t="n">
-        <v>117.0228591743913</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="G15" t="n">
-        <v>117.0228591743913</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="H15" t="n">
-        <v>17.83999999999986</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="I15" t="n">
-        <v>37.22793038452707</v>
+        <v>37.22793038452531</v>
       </c>
       <c r="J15" t="n">
-        <v>250.1893612430617</v>
+        <v>37.22793038452531</v>
       </c>
       <c r="K15" t="n">
-        <v>278.5017834113636</v>
+        <v>257.9979303845257</v>
       </c>
       <c r="L15" t="n">
-        <v>343.1892811566467</v>
+        <v>340.6798698950636</v>
       </c>
       <c r="M15" t="n">
-        <v>393.2191506736996</v>
+        <v>390.7097394121165</v>
       </c>
       <c r="N15" t="n">
-        <v>482.3558220608763</v>
+        <v>479.8464107992933</v>
       </c>
       <c r="O15" t="n">
         <v>700.6164107992937</v>
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>103.5865395833778</v>
+        <v>115.3934682565156</v>
       </c>
       <c r="C16" t="n">
-        <v>103.5865395833778</v>
+        <v>68.19624942010687</v>
       </c>
       <c r="D16" t="n">
-        <v>103.5865395833778</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="E16" t="n">
-        <v>85.24835332613756</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="F16" t="n">
-        <v>36.37678164154975</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="G16" t="n">
-        <v>17.83999999999764</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="H16" t="n">
-        <v>21.19160942169029</v>
+        <v>21.19160942169075</v>
       </c>
       <c r="I16" t="n">
-        <v>90.68037819383878</v>
+        <v>90.68037819383923</v>
       </c>
       <c r="J16" t="n">
-        <v>311.4503781938391</v>
+        <v>311.4503781938396</v>
       </c>
       <c r="K16" t="n">
-        <v>329.2014481962813</v>
+        <v>329.2014481962817</v>
       </c>
       <c r="L16" t="n">
-        <v>233.6480566144874</v>
+        <v>329.2014481962817</v>
       </c>
       <c r="M16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="N16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="O16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="P16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="Q16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="R16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="S16" t="n">
-        <v>45.68289192570546</v>
+        <v>141.2362835074997</v>
       </c>
       <c r="T16" t="n">
-        <v>64.42767272385458</v>
+        <v>159.9810643056489</v>
       </c>
       <c r="U16" t="n">
-        <v>138.7562581490265</v>
+        <v>234.3096497308208</v>
       </c>
       <c r="V16" t="n">
-        <v>165.3176510349724</v>
+        <v>260.8710426167667</v>
       </c>
       <c r="W16" t="n">
-        <v>165.3176510349724</v>
+        <v>260.8710426167667</v>
       </c>
       <c r="X16" t="n">
-        <v>165.3176510349724</v>
+        <v>239.2107947075672</v>
       </c>
       <c r="Y16" t="n">
-        <v>165.3176510349724</v>
+        <v>177.1245797081102</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>666.7474747474772</v>
+        <v>243.0925252525233</v>
       </c>
       <c r="C17" t="n">
-        <v>666.7474747474772</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="D17" t="n">
-        <v>546.5803727052594</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="E17" t="n">
-        <v>366.4154337084223</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="F17" t="n">
-        <v>185.7188390538649</v>
+        <v>17.83999999999946</v>
       </c>
       <c r="G17" t="n">
-        <v>185.7188390538649</v>
+        <v>17.83999999999946</v>
       </c>
       <c r="H17" t="n">
-        <v>17.8399999999998</v>
+        <v>17.83999999999995</v>
       </c>
       <c r="I17" t="n">
-        <v>17.83999999999855</v>
+        <v>17.83999999999946</v>
       </c>
       <c r="J17" t="n">
-        <v>112.8583978877109</v>
+        <v>112.8583978877118</v>
       </c>
       <c r="K17" t="n">
-        <v>307.2615239178616</v>
+        <v>307.2615239178626</v>
       </c>
       <c r="L17" t="n">
-        <v>528.0315239178624</v>
+        <v>528.0315239178631</v>
       </c>
       <c r="M17" t="n">
-        <v>528.0315239178624</v>
+        <v>484.5625797156135</v>
       </c>
       <c r="N17" t="n">
-        <v>484.562579715614</v>
+        <v>484.5625797156135</v>
       </c>
       <c r="O17" t="n">
-        <v>672.5154127568604</v>
+        <v>672.51541275686</v>
       </c>
       <c r="P17" t="n">
-        <v>892.000000000003</v>
+        <v>892.0000000000025</v>
       </c>
       <c r="Q17" t="n">
-        <v>892.000000000003</v>
+        <v>892.0000000000025</v>
       </c>
       <c r="R17" t="n">
-        <v>892.000000000003</v>
+        <v>892.0000000000025</v>
       </c>
       <c r="S17" t="n">
-        <v>892.000000000003</v>
+        <v>892.0000000000025</v>
       </c>
       <c r="T17" t="n">
-        <v>892.000000000003</v>
+        <v>666.7474747474769</v>
       </c>
       <c r="U17" t="n">
-        <v>892.000000000003</v>
+        <v>666.7474747474769</v>
       </c>
       <c r="V17" t="n">
-        <v>892.000000000003</v>
+        <v>468.345050505049</v>
       </c>
       <c r="W17" t="n">
-        <v>892.000000000003</v>
+        <v>468.345050505049</v>
       </c>
       <c r="X17" t="n">
-        <v>892.000000000003</v>
+        <v>468.345050505049</v>
       </c>
       <c r="Y17" t="n">
-        <v>892.000000000003</v>
+        <v>468.345050505049</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>253.4874172001657</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="C18" t="n">
-        <v>117.0228591743887</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="D18" t="n">
-        <v>117.0228591743887</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="E18" t="n">
-        <v>117.0228591743887</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="F18" t="n">
-        <v>117.0228591743887</v>
+        <v>17.8399999999981</v>
       </c>
       <c r="G18" t="n">
-        <v>117.0228591743887</v>
+        <v>17.83999999999946</v>
       </c>
       <c r="H18" t="n">
-        <v>17.83999999999719</v>
+        <v>17.83999999999992</v>
       </c>
       <c r="I18" t="n">
-        <v>37.2279303845244</v>
+        <v>37.22793038452713</v>
       </c>
       <c r="J18" t="n">
-        <v>236.9893235984827</v>
+        <v>37.22793038452713</v>
       </c>
       <c r="K18" t="n">
-        <v>265.3017457667846</v>
+        <v>65.54035255282905</v>
       </c>
       <c r="L18" t="n">
-        <v>412.7140978921427</v>
+        <v>286.3103525528294</v>
       </c>
       <c r="M18" t="n">
-        <v>462.7439674091956</v>
+        <v>373.6072960220184</v>
       </c>
       <c r="N18" t="n">
-        <v>462.7439674091956</v>
+        <v>462.7439674091952</v>
       </c>
       <c r="O18" t="n">
-        <v>683.5139674091961</v>
+        <v>683.5139674091956</v>
       </c>
       <c r="P18" t="n">
-        <v>735.2294475339173</v>
+        <v>735.2294475339169</v>
       </c>
       <c r="Q18" t="n">
-        <v>892.000000000003</v>
+        <v>892.0000000000025</v>
       </c>
       <c r="R18" t="n">
-        <v>892.000000000003</v>
+        <v>892.0000000000025</v>
       </c>
       <c r="S18" t="n">
-        <v>666.7474747474772</v>
+        <v>666.7474747474769</v>
       </c>
       <c r="T18" t="n">
-        <v>488.9408508380388</v>
+        <v>488.9408508380385</v>
       </c>
       <c r="U18" t="n">
-        <v>449.3083661349007</v>
+        <v>373.8190869613251</v>
       </c>
       <c r="V18" t="n">
-        <v>449.3083661349007</v>
+        <v>373.8190869613251</v>
       </c>
       <c r="W18" t="n">
-        <v>449.3083661349007</v>
+        <v>373.8190869613251</v>
       </c>
       <c r="X18" t="n">
-        <v>253.4874172001657</v>
+        <v>177.9981380265902</v>
       </c>
       <c r="Y18" t="n">
-        <v>253.4874172001657</v>
+        <v>177.9981380265902</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>137.4747591092642</v>
+        <v>229.5826520285821</v>
       </c>
       <c r="C19" t="n">
-        <v>137.4747591092642</v>
+        <v>182.3854331921734</v>
       </c>
       <c r="D19" t="n">
-        <v>137.4747591092642</v>
+        <v>122.2478391966628</v>
       </c>
       <c r="E19" t="n">
-        <v>137.4747591092642</v>
+        <v>66.71157168458546</v>
       </c>
       <c r="F19" t="n">
-        <v>137.4747591092642</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="G19" t="n">
-        <v>137.4747591092642</v>
+        <v>17.83999999999764</v>
       </c>
       <c r="H19" t="n">
-        <v>140.8263685309568</v>
+        <v>21.19160942169029</v>
       </c>
       <c r="I19" t="n">
-        <v>210.3151373031053</v>
+        <v>90.68037819383878</v>
       </c>
       <c r="J19" t="n">
-        <v>431.0851373031058</v>
+        <v>311.4503781938391</v>
       </c>
       <c r="K19" t="n">
-        <v>448.8362073055479</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="L19" t="n">
-        <v>431.0576899413049</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="M19" t="n">
-        <v>243.092525252523</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="N19" t="n">
-        <v>17.83999999999719</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="O19" t="n">
-        <v>17.83999999999719</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="P19" t="n">
-        <v>17.83999999999719</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.83999999999719</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="R19" t="n">
-        <v>17.83999999999719</v>
+        <v>329.2014481962813</v>
       </c>
       <c r="S19" t="n">
-        <v>17.83999999999719</v>
+        <v>233.7652193703667</v>
       </c>
       <c r="T19" t="n">
-        <v>36.58478079814631</v>
+        <v>252.5100001685158</v>
       </c>
       <c r="U19" t="n">
-        <v>110.9133662233182</v>
+        <v>326.8385855936877</v>
       </c>
       <c r="V19" t="n">
-        <v>137.4747591092642</v>
+        <v>353.3999784796337</v>
       </c>
       <c r="W19" t="n">
-        <v>137.4747591092642</v>
+        <v>353.3999784796337</v>
       </c>
       <c r="X19" t="n">
-        <v>137.4747591092642</v>
+        <v>353.3999784796337</v>
       </c>
       <c r="Y19" t="n">
-        <v>137.4747591092642</v>
+        <v>291.3137634801767</v>
       </c>
     </row>
     <row r="20">
@@ -5719,40 +5719,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.83999999999719</v>
+        <v>441.4949494949515</v>
       </c>
       <c r="C20" t="n">
-        <v>17.83999999999719</v>
+        <v>441.4949494949515</v>
       </c>
       <c r="D20" t="n">
-        <v>17.83999999999719</v>
+        <v>441.4949494949515</v>
       </c>
       <c r="E20" t="n">
-        <v>17.83999999999719</v>
+        <v>261.3300104981145</v>
       </c>
       <c r="F20" t="n">
-        <v>17.83999999999833</v>
+        <v>195.8335895899507</v>
       </c>
       <c r="G20" t="n">
-        <v>17.83999999999995</v>
+        <v>17.83999999999986</v>
       </c>
       <c r="H20" t="n">
-        <v>17.83999999999995</v>
+        <v>17.83999999999986</v>
       </c>
       <c r="I20" t="n">
-        <v>17.83999999999995</v>
+        <v>17.83999999999901</v>
       </c>
       <c r="J20" t="n">
-        <v>112.8583978877123</v>
+        <v>112.8583978877113</v>
       </c>
       <c r="K20" t="n">
-        <v>307.261523917863</v>
+        <v>307.2615239178621</v>
       </c>
       <c r="L20" t="n">
-        <v>528.0315239178635</v>
+        <v>528.0315239178628</v>
       </c>
       <c r="M20" t="n">
-        <v>523.6236504673867</v>
+        <v>484.562579715614</v>
       </c>
       <c r="N20" t="n">
         <v>484.562579715614</v>
@@ -5779,16 +5779,16 @@
         <v>666.7474747474772</v>
       </c>
       <c r="V20" t="n">
-        <v>441.4949494949515</v>
+        <v>666.7474747474772</v>
       </c>
       <c r="W20" t="n">
-        <v>216.2424242424257</v>
+        <v>666.7474747474772</v>
       </c>
       <c r="X20" t="n">
-        <v>216.2424242424257</v>
+        <v>666.7474747474772</v>
       </c>
       <c r="Y20" t="n">
-        <v>216.2424242424257</v>
+        <v>666.7474747474772</v>
       </c>
     </row>
     <row r="21">
@@ -5798,49 +5798,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>395.3245419849843</v>
+        <v>152.86754095534</v>
       </c>
       <c r="C21" t="n">
-        <v>258.8599839592072</v>
+        <v>17.83999999999975</v>
       </c>
       <c r="D21" t="n">
-        <v>135.6906032544571</v>
+        <v>17.83999999999975</v>
       </c>
       <c r="E21" t="n">
-        <v>17.83999999999989</v>
+        <v>17.83999999999975</v>
       </c>
       <c r="F21" t="n">
-        <v>17.83999999999989</v>
+        <v>17.83999999999975</v>
       </c>
       <c r="G21" t="n">
-        <v>17.83999999999989</v>
+        <v>17.83999999999975</v>
       </c>
       <c r="H21" t="n">
-        <v>17.83999999999989</v>
+        <v>17.83999999999975</v>
       </c>
       <c r="I21" t="n">
-        <v>37.2279303845271</v>
+        <v>37.22793038452696</v>
       </c>
       <c r="J21" t="n">
-        <v>236.9893235984854</v>
+        <v>257.9979303845274</v>
       </c>
       <c r="K21" t="n">
-        <v>265.3017457667873</v>
+        <v>286.3103525528293</v>
       </c>
       <c r="L21" t="n">
-        <v>480.3479789710514</v>
+        <v>350.9978502981124</v>
       </c>
       <c r="M21" t="n">
-        <v>530.3778484881043</v>
+        <v>401.0277198151653</v>
       </c>
       <c r="N21" t="n">
-        <v>619.5145198752812</v>
+        <v>490.1643912023421</v>
       </c>
       <c r="O21" t="n">
-        <v>840.2845198752817</v>
+        <v>544.9041216958078</v>
       </c>
       <c r="P21" t="n">
-        <v>892.000000000003</v>
+        <v>752.3318909240154</v>
       </c>
       <c r="Q21" t="n">
         <v>892.000000000003</v>
@@ -5855,19 +5855,19 @@
         <v>488.9408508380388</v>
       </c>
       <c r="U21" t="n">
-        <v>488.9408508380388</v>
+        <v>313.0256789819325</v>
       </c>
       <c r="V21" t="n">
-        <v>488.9408508380388</v>
+        <v>313.0256789819325</v>
       </c>
       <c r="W21" t="n">
-        <v>395.3245419849843</v>
+        <v>313.0256789819325</v>
       </c>
       <c r="X21" t="n">
-        <v>395.3245419849843</v>
+        <v>313.0256789819325</v>
       </c>
       <c r="Y21" t="n">
-        <v>395.3245419849843</v>
+        <v>313.0256789819325</v>
       </c>
     </row>
     <row r="22">
@@ -5889,43 +5889,43 @@
         <v>137.4747591092642</v>
       </c>
       <c r="F22" t="n">
-        <v>88.60318742467635</v>
+        <v>137.4747591092642</v>
       </c>
       <c r="G22" t="n">
-        <v>70.06640578312424</v>
+        <v>137.4747591092642</v>
       </c>
       <c r="H22" t="n">
-        <v>73.4180152048169</v>
+        <v>140.8263685309568</v>
       </c>
       <c r="I22" t="n">
-        <v>142.9067839769654</v>
+        <v>210.3151373031053</v>
       </c>
       <c r="J22" t="n">
-        <v>363.6767839769659</v>
+        <v>431.0851373031058</v>
       </c>
       <c r="K22" t="n">
-        <v>381.427853979408</v>
+        <v>448.8362073055479</v>
       </c>
       <c r="L22" t="n">
-        <v>285.8744623976143</v>
+        <v>431.0576899413049</v>
       </c>
       <c r="M22" t="n">
-        <v>143.4014217896012</v>
+        <v>243.092525252523</v>
       </c>
       <c r="N22" t="n">
-        <v>143.4014217896012</v>
+        <v>17.83999999999719</v>
       </c>
       <c r="O22" t="n">
-        <v>143.4014217896012</v>
+        <v>17.83999999999719</v>
       </c>
       <c r="P22" t="n">
-        <v>143.4014217896012</v>
+        <v>17.83999999999719</v>
       </c>
       <c r="Q22" t="n">
-        <v>143.4014217896012</v>
+        <v>17.83999999999719</v>
       </c>
       <c r="R22" t="n">
-        <v>143.4014217896012</v>
+        <v>17.83999999999719</v>
       </c>
       <c r="S22" t="n">
         <v>17.83999999999719</v>
@@ -5968,10 +5968,10 @@
         <v>17.83999999999673</v>
       </c>
       <c r="F23" t="n">
-        <v>17.8399999999981</v>
+        <v>17.83999999999742</v>
       </c>
       <c r="G23" t="n">
-        <v>17.83999999999969</v>
+        <v>17.83999999999924</v>
       </c>
       <c r="H23" t="n">
         <v>17.83999999999995</v>
@@ -5986,10 +5986,10 @@
         <v>307.2615239178623</v>
       </c>
       <c r="L23" t="n">
-        <v>528.0315239178626</v>
+        <v>528.0315239178632</v>
       </c>
       <c r="M23" t="n">
-        <v>528.0315239178626</v>
+        <v>484.5625797156144</v>
       </c>
       <c r="N23" t="n">
         <v>484.5625797156144</v>
@@ -6035,34 +6035,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>298.5260354930693</v>
+        <v>313.7980298621459</v>
       </c>
       <c r="C24" t="n">
-        <v>298.5260354930693</v>
+        <v>313.7980298621459</v>
       </c>
       <c r="D24" t="n">
-        <v>298.5260354930693</v>
+        <v>250.4746864240297</v>
       </c>
       <c r="E24" t="n">
-        <v>232.5367837866193</v>
+        <v>132.6240831695725</v>
       </c>
       <c r="F24" t="n">
-        <v>117.7527006170467</v>
+        <v>17.83999999999989</v>
       </c>
       <c r="G24" t="n">
-        <v>17.83999999999986</v>
+        <v>17.83999999999989</v>
       </c>
       <c r="H24" t="n">
-        <v>17.83999999999986</v>
+        <v>17.83999999999989</v>
       </c>
       <c r="I24" t="n">
-        <v>37.22793038452707</v>
+        <v>37.2279303845271</v>
       </c>
       <c r="J24" t="n">
-        <v>236.9893235984853</v>
+        <v>236.9893235984854</v>
       </c>
       <c r="K24" t="n">
-        <v>265.3017457667872</v>
+        <v>265.3017457667873</v>
       </c>
       <c r="L24" t="n">
         <v>340.6798698950643</v>
@@ -6095,16 +6095,16 @@
         <v>488.9408508380392</v>
       </c>
       <c r="V24" t="n">
-        <v>298.5260354930693</v>
+        <v>488.9408508380392</v>
       </c>
       <c r="W24" t="n">
-        <v>298.5260354930693</v>
+        <v>488.9408508380392</v>
       </c>
       <c r="X24" t="n">
-        <v>298.5260354930693</v>
+        <v>488.9408508380392</v>
       </c>
       <c r="Y24" t="n">
-        <v>298.5260354930693</v>
+        <v>313.7980298621459</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>177.4796832559714</v>
+        <v>54.08339974846957</v>
       </c>
       <c r="C25" t="n">
-        <v>177.4796832559714</v>
+        <v>54.08339974846957</v>
       </c>
       <c r="D25" t="n">
-        <v>117.3420892604608</v>
+        <v>54.08339974846957</v>
       </c>
       <c r="E25" t="n">
-        <v>61.80582174838351</v>
+        <v>54.08339974846957</v>
       </c>
       <c r="F25" t="n">
+        <v>20.00513828209883</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20.00513828209883</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.35674770379148</v>
+      </c>
+      <c r="I25" t="n">
+        <v>92.84551647593997</v>
+      </c>
+      <c r="J25" t="n">
+        <v>313.6155164759406</v>
+      </c>
+      <c r="K25" t="n">
+        <v>331.3665864783827</v>
+      </c>
+      <c r="L25" t="n">
+        <v>331.3665864783827</v>
+      </c>
+      <c r="M25" t="n">
+        <v>143.4014217896007</v>
+      </c>
+      <c r="N25" t="n">
+        <v>143.4014217896007</v>
+      </c>
+      <c r="O25" t="n">
+        <v>143.4014217896007</v>
+      </c>
+      <c r="P25" t="n">
+        <v>143.4014217896007</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>143.4014217896007</v>
+      </c>
+      <c r="R25" t="n">
+        <v>143.4014217896007</v>
+      </c>
+      <c r="S25" t="n">
         <v>17.83999999999673</v>
       </c>
-      <c r="G25" t="n">
-        <v>17.83999999999673</v>
-      </c>
-      <c r="H25" t="n">
-        <v>21.19160942168939</v>
-      </c>
-      <c r="I25" t="n">
-        <v>90.68037819383787</v>
-      </c>
-      <c r="J25" t="n">
-        <v>311.4503781938384</v>
-      </c>
-      <c r="K25" t="n">
-        <v>329.2014481962806</v>
-      </c>
-      <c r="L25" t="n">
-        <v>329.2014481962806</v>
-      </c>
-      <c r="M25" t="n">
-        <v>141.2362835074986</v>
-      </c>
-      <c r="N25" t="n">
-        <v>141.2362835074986</v>
-      </c>
-      <c r="O25" t="n">
-        <v>141.2362835074986</v>
-      </c>
-      <c r="P25" t="n">
-        <v>141.2362835074986</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>141.2362835074986</v>
-      </c>
-      <c r="R25" t="n">
-        <v>141.2362835074986</v>
-      </c>
-      <c r="S25" t="n">
-        <v>141.2362835074986</v>
-      </c>
       <c r="T25" t="n">
-        <v>159.9810643056477</v>
+        <v>36.58478079814586</v>
       </c>
       <c r="U25" t="n">
-        <v>234.3096497308196</v>
+        <v>110.9133662233177</v>
       </c>
       <c r="V25" t="n">
-        <v>260.8710426167656</v>
+        <v>137.4747591092637</v>
       </c>
       <c r="W25" t="n">
-        <v>260.8710426167656</v>
+        <v>137.4747591092637</v>
       </c>
       <c r="X25" t="n">
-        <v>239.210794707566</v>
+        <v>115.8145112000642</v>
       </c>
       <c r="Y25" t="n">
-        <v>239.210794707566</v>
+        <v>115.8145112000642</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>565.0909090909101</v>
+        <v>374.1818181818192</v>
       </c>
       <c r="C26" t="n">
-        <v>374.1818181818192</v>
+        <v>183.2727272727283</v>
       </c>
       <c r="D26" t="n">
-        <v>206.0290909090899</v>
+        <v>183.2727272727283</v>
       </c>
       <c r="E26" t="n">
-        <v>206.0290909090899</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="F26" t="n">
-        <v>206.0290909090899</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="G26" t="n">
-        <v>15.11999999999898</v>
+        <v>15.11999999999944</v>
       </c>
       <c r="H26" t="n">
-        <v>15.11999999999898</v>
+        <v>15.11999999999944</v>
       </c>
       <c r="I26" t="n">
         <v>15.11999999999898</v>
@@ -6247,22 +6247,22 @@
         <v>756.000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>756.000000000001</v>
+        <v>565.0909090909101</v>
       </c>
       <c r="U26" t="n">
-        <v>756.000000000001</v>
+        <v>565.0909090909101</v>
       </c>
       <c r="V26" t="n">
-        <v>756.000000000001</v>
+        <v>565.0909090909101</v>
       </c>
       <c r="W26" t="n">
-        <v>756.000000000001</v>
+        <v>374.1818181818192</v>
       </c>
       <c r="X26" t="n">
-        <v>756.000000000001</v>
+        <v>374.1818181818192</v>
       </c>
       <c r="Y26" t="n">
-        <v>756.000000000001</v>
+        <v>374.1818181818192</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>681.0469830943315</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="C27" t="n">
-        <v>681.0469830943315</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="D27" t="n">
-        <v>535.6553801673591</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="E27" t="n">
-        <v>535.6553801673591</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="F27" t="n">
-        <v>398.6490747755643</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="G27" t="n">
-        <v>276.5141519362952</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="H27" t="n">
-        <v>276.5141519362952</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="I27" t="n">
-        <v>276.5141519362952</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="J27" t="n">
-        <v>343.0502194880119</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="K27" t="n">
-        <v>371.3626416563138</v>
+        <v>43.4324221683009</v>
       </c>
       <c r="L27" t="n">
-        <v>436.0501394015969</v>
+        <v>230.5424221683009</v>
       </c>
       <c r="M27" t="n">
-        <v>464.3000089186497</v>
+        <v>258.7922916853537</v>
       </c>
       <c r="N27" t="n">
-        <v>531.6566803058265</v>
+        <v>258.7922916853537</v>
       </c>
       <c r="O27" t="n">
-        <v>586.3964107992922</v>
+        <v>313.5320221788195</v>
       </c>
       <c r="P27" t="n">
-        <v>638.1118909240134</v>
+        <v>365.2475023035407</v>
       </c>
       <c r="Q27" t="n">
-        <v>756.000000000001</v>
+        <v>480.1232477185794</v>
       </c>
       <c r="R27" t="n">
-        <v>756.000000000001</v>
+        <v>480.1232477185794</v>
       </c>
       <c r="S27" t="n">
-        <v>756.000000000001</v>
+        <v>480.1232477185794</v>
       </c>
       <c r="T27" t="n">
-        <v>756.000000000001</v>
+        <v>480.1232477185794</v>
       </c>
       <c r="U27" t="n">
-        <v>756.000000000001</v>
+        <v>396.9381818181809</v>
       </c>
       <c r="V27" t="n">
-        <v>756.000000000001</v>
+        <v>206.0290909090899</v>
       </c>
       <c r="W27" t="n">
-        <v>756.000000000001</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="X27" t="n">
-        <v>756.000000000001</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="Y27" t="n">
-        <v>756.000000000001</v>
+        <v>15.11999999999898</v>
       </c>
     </row>
     <row r="28">
@@ -6366,40 +6366,40 @@
         <v>756.000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>756.000000000001</v>
+        <v>725.632679837667</v>
       </c>
       <c r="H28" t="n">
-        <v>756.000000000001</v>
+        <v>725.632679837667</v>
       </c>
       <c r="I28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="J28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="K28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="L28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="M28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="N28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="O28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="P28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="Q28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="R28" t="n">
-        <v>756.000000000001</v>
+        <v>751.2186071140551</v>
       </c>
       <c r="S28" t="n">
         <v>751.2186071140551</v>
@@ -6430,40 +6430,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>565.0909090909104</v>
+        <v>183.2727272727282</v>
       </c>
       <c r="C29" t="n">
-        <v>565.0909090909104</v>
+        <v>15.11999999999853</v>
       </c>
       <c r="D29" t="n">
-        <v>374.1818181818193</v>
+        <v>15.11999999999989</v>
       </c>
       <c r="E29" t="n">
-        <v>205.9176047555665</v>
+        <v>15.11999999999989</v>
       </c>
       <c r="F29" t="n">
-        <v>15.11999999999898</v>
+        <v>15.11999999999989</v>
       </c>
       <c r="G29" t="n">
-        <v>15.11999999999932</v>
+        <v>15.11999999999989</v>
       </c>
       <c r="H29" t="n">
         <v>15.11999999999989</v>
       </c>
       <c r="I29" t="n">
-        <v>15.11999999999932</v>
+        <v>15.11999999999989</v>
       </c>
       <c r="J29" t="n">
-        <v>110.1383978877117</v>
+        <v>110.1383978877122</v>
       </c>
       <c r="K29" t="n">
-        <v>297.2483978877119</v>
+        <v>297.2483978877125</v>
       </c>
       <c r="L29" t="n">
-        <v>484.3583978877121</v>
+        <v>484.3583978877126</v>
       </c>
       <c r="M29" t="n">
-        <v>381.7800000000012</v>
+        <v>426.5819834883362</v>
       </c>
       <c r="N29" t="n">
         <v>381.7800000000012</v>
@@ -6484,22 +6484,22 @@
         <v>756.0000000000015</v>
       </c>
       <c r="T29" t="n">
-        <v>756.0000000000015</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="U29" t="n">
-        <v>756.0000000000015</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="V29" t="n">
-        <v>756.0000000000015</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="W29" t="n">
-        <v>756.0000000000015</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="X29" t="n">
-        <v>756.0000000000015</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="Y29" t="n">
-        <v>756.0000000000015</v>
+        <v>183.2727272727282</v>
       </c>
     </row>
     <row r="30">
@@ -6509,49 +6509,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>161.6855681267857</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="C30" t="n">
-        <v>15.11999999999853</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="D30" t="n">
-        <v>15.11999999999853</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="E30" t="n">
-        <v>15.11999999999978</v>
+        <v>249.288962545984</v>
       </c>
       <c r="F30" t="n">
-        <v>15.11999999999978</v>
+        <v>124.4038692754013</v>
       </c>
       <c r="G30" t="n">
-        <v>15.11999999999978</v>
+        <v>124.4038692754013</v>
       </c>
       <c r="H30" t="n">
         <v>15.11999999999978</v>
       </c>
       <c r="I30" t="n">
-        <v>24.60793038452699</v>
+        <v>42.15823645813077</v>
       </c>
       <c r="J30" t="n">
-        <v>211.7179303845271</v>
+        <v>229.2682364581309</v>
       </c>
       <c r="K30" t="n">
-        <v>240.030352552829</v>
+        <v>257.5806586264328</v>
       </c>
       <c r="L30" t="n">
-        <v>304.7178502981121</v>
+        <v>322.2681563717159</v>
       </c>
       <c r="M30" t="n">
-        <v>304.7178502981121</v>
+        <v>362.3980258887687</v>
       </c>
       <c r="N30" t="n">
-        <v>383.9545216852889</v>
+        <v>441.6346972759455</v>
       </c>
       <c r="O30" t="n">
-        <v>438.6942521787547</v>
+        <v>557.4139674091947</v>
       </c>
       <c r="P30" t="n">
-        <v>625.8042521787547</v>
+        <v>609.1294475339159</v>
       </c>
       <c r="Q30" t="n">
         <v>756.0000000000015</v>
@@ -6569,16 +6569,16 @@
         <v>374.1818181818193</v>
       </c>
       <c r="V30" t="n">
-        <v>183.2727272727282</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="W30" t="n">
-        <v>183.2727272727282</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="X30" t="n">
-        <v>183.2727272727282</v>
+        <v>374.1818181818193</v>
       </c>
       <c r="Y30" t="n">
-        <v>183.2727272727282</v>
+        <v>374.1818181818193</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="C31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="D31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="E31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="F31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="G31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="H31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="I31" t="n">
-        <v>164.643527881414</v>
+        <v>561.0389299975592</v>
       </c>
       <c r="J31" t="n">
-        <v>351.7535278814141</v>
+        <v>748.1489299975593</v>
       </c>
       <c r="K31" t="n">
-        <v>359.6045978838563</v>
+        <v>756.0000000000015</v>
       </c>
       <c r="L31" t="n">
-        <v>253.9501962010524</v>
+        <v>756.0000000000015</v>
       </c>
       <c r="M31" t="n">
-        <v>63.04110529196129</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="N31" t="n">
-        <v>63.04110529196129</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="O31" t="n">
-        <v>63.04110529196129</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="P31" t="n">
-        <v>63.04110529196129</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="Q31" t="n">
-        <v>63.04110529196129</v>
+        <v>565.0909090909104</v>
       </c>
       <c r="R31" t="n">
-        <v>63.04110529196129</v>
+        <v>411.5154021161437</v>
       </c>
       <c r="S31" t="n">
-        <v>15.11999999999853</v>
+        <v>411.5154021161437</v>
       </c>
       <c r="T31" t="n">
-        <v>23.96478079814765</v>
+        <v>420.3601829142929</v>
       </c>
       <c r="U31" t="n">
-        <v>88.39336622331953</v>
+        <v>484.7887683394648</v>
       </c>
       <c r="V31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="W31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="X31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
       <c r="Y31" t="n">
-        <v>105.0547591092655</v>
+        <v>501.4501612254107</v>
       </c>
     </row>
     <row r="32">
@@ -6667,37 +6667,37 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>183.2727272727283</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="C32" t="n">
         <v>15.11999999999807</v>
       </c>
       <c r="D32" t="n">
-        <v>15.11999999999992</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="E32" t="n">
-        <v>15.11999999999992</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="F32" t="n">
-        <v>15.11999999999992</v>
+        <v>15.11999999999853</v>
       </c>
       <c r="G32" t="n">
-        <v>15.11999999999992</v>
+        <v>15.11999999999955</v>
       </c>
       <c r="H32" t="n">
-        <v>15.11999999999992</v>
+        <v>15.11999999999995</v>
       </c>
       <c r="I32" t="n">
-        <v>15.11999999999992</v>
+        <v>15.11999999999995</v>
       </c>
       <c r="J32" t="n">
         <v>110.1383978877123</v>
       </c>
       <c r="K32" t="n">
-        <v>297.2483978877125</v>
+        <v>297.2483978877124</v>
       </c>
       <c r="L32" t="n">
-        <v>484.3583978877127</v>
+        <v>484.3583978877124</v>
       </c>
       <c r="M32" t="n">
         <v>381.7800000000015</v>
@@ -6721,22 +6721,22 @@
         <v>756.0000000000019</v>
       </c>
       <c r="T32" t="n">
-        <v>565.0909090909107</v>
+        <v>756.0000000000019</v>
       </c>
       <c r="U32" t="n">
         <v>565.0909090909107</v>
       </c>
       <c r="V32" t="n">
-        <v>565.0909090909107</v>
+        <v>374.1818181818195</v>
       </c>
       <c r="W32" t="n">
-        <v>374.1818181818195</v>
+        <v>183.2727272727283</v>
       </c>
       <c r="X32" t="n">
-        <v>374.1818181818195</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="Y32" t="n">
-        <v>183.2727272727283</v>
+        <v>15.11999999999807</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>252.3554826308688</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="C33" t="n">
-        <v>252.3554826308688</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="D33" t="n">
-        <v>252.3554826308688</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="E33" t="n">
-        <v>124.4038692754015</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="F33" t="n">
-        <v>124.4038692754015</v>
+        <v>15.11999999999853</v>
       </c>
       <c r="G33" t="n">
-        <v>124.4038692754015</v>
+        <v>15.11999999999989</v>
       </c>
       <c r="H33" t="n">
         <v>15.11999999999989</v>
@@ -6770,52 +6770,52 @@
         <v>24.6079303845271</v>
       </c>
       <c r="J33" t="n">
-        <v>24.6079303845271</v>
+        <v>211.7179303845273</v>
       </c>
       <c r="K33" t="n">
-        <v>149.1542566178215</v>
+        <v>335.7226416563147</v>
       </c>
       <c r="L33" t="n">
-        <v>213.8417543631045</v>
+        <v>400.4101394015978</v>
       </c>
       <c r="M33" t="n">
-        <v>253.9716238801574</v>
+        <v>440.5400089186506</v>
       </c>
       <c r="N33" t="n">
-        <v>333.2082952673342</v>
+        <v>519.7766803058274</v>
       </c>
       <c r="O33" t="n">
-        <v>422.0194475339161</v>
+        <v>574.5164107992931</v>
       </c>
       <c r="P33" t="n">
-        <v>609.1294475339164</v>
+        <v>626.2318909240144</v>
       </c>
       <c r="Q33" t="n">
         <v>756.0000000000019</v>
       </c>
       <c r="R33" t="n">
+        <v>756.0000000000019</v>
+      </c>
+      <c r="S33" t="n">
         <v>565.0909090909107</v>
       </c>
-      <c r="S33" t="n">
-        <v>374.1818181818195</v>
-      </c>
       <c r="T33" t="n">
-        <v>374.1818181818195</v>
+        <v>565.0909090909107</v>
       </c>
       <c r="U33" t="n">
-        <v>374.1818181818195</v>
+        <v>565.0909090909107</v>
       </c>
       <c r="V33" t="n">
         <v>374.1818181818195</v>
       </c>
       <c r="W33" t="n">
-        <v>374.1818181818195</v>
+        <v>183.2727272727283</v>
       </c>
       <c r="X33" t="n">
-        <v>374.1818181818195</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="Y33" t="n">
-        <v>374.1818181818195</v>
+        <v>15.11999999999807</v>
       </c>
     </row>
     <row r="34">
@@ -6867,7 +6867,7 @@
         <v>565.0909090909107</v>
       </c>
       <c r="P34" t="n">
-        <v>565.0909090909107</v>
+        <v>411.5154021161441</v>
       </c>
       <c r="Q34" t="n">
         <v>411.5154021161441</v>
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15.11999999999978</v>
+        <v>206.0290909090889</v>
       </c>
       <c r="C35" t="n">
-        <v>15.11999999999978</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="D35" t="n">
         <v>15.11999999999978</v>
@@ -6925,19 +6925,19 @@
         <v>15.11999999999978</v>
       </c>
       <c r="I35" t="n">
-        <v>15.11999999999887</v>
+        <v>15.11999999999978</v>
       </c>
       <c r="J35" t="n">
-        <v>110.1383978877112</v>
+        <v>110.1383978877121</v>
       </c>
       <c r="K35" t="n">
-        <v>297.2483978877115</v>
+        <v>297.2483978877124</v>
       </c>
       <c r="L35" t="n">
-        <v>484.3583978877116</v>
+        <v>484.3583978877126</v>
       </c>
       <c r="M35" t="n">
-        <v>426.5819834883353</v>
+        <v>381.7800000000017</v>
       </c>
       <c r="N35" t="n">
         <v>381.7800000000017</v>
@@ -6955,25 +6955,25 @@
         <v>756.0000000000024</v>
       </c>
       <c r="S35" t="n">
-        <v>756.0000000000024</v>
+        <v>565.0909090909111</v>
       </c>
       <c r="T35" t="n">
-        <v>756.0000000000024</v>
+        <v>396.9381818181802</v>
       </c>
       <c r="U35" t="n">
-        <v>587.8472727272737</v>
+        <v>396.9381818181802</v>
       </c>
       <c r="V35" t="n">
-        <v>396.9381818181824</v>
+        <v>396.9381818181802</v>
       </c>
       <c r="W35" t="n">
-        <v>206.0290909090911</v>
+        <v>396.9381818181802</v>
       </c>
       <c r="X35" t="n">
-        <v>15.11999999999978</v>
+        <v>396.9381818181802</v>
       </c>
       <c r="Y35" t="n">
-        <v>15.11999999999978</v>
+        <v>206.0290909090889</v>
       </c>
     </row>
     <row r="36">
@@ -6998,31 +6998,31 @@
         <v>15.11999999999716</v>
       </c>
       <c r="G36" t="n">
-        <v>15.11999999999875</v>
+        <v>15.11999999999807</v>
       </c>
       <c r="H36" t="n">
-        <v>15.11999999999966</v>
+        <v>15.11999999999955</v>
       </c>
       <c r="I36" t="n">
-        <v>24.60793038452687</v>
+        <v>24.60793038452676</v>
       </c>
       <c r="J36" t="n">
-        <v>211.7179303845272</v>
+        <v>147.5175546195526</v>
       </c>
       <c r="K36" t="n">
-        <v>240.0303525528292</v>
+        <v>175.8299767878545</v>
       </c>
       <c r="L36" t="n">
-        <v>400.4101394015983</v>
+        <v>240.5174745331376</v>
       </c>
       <c r="M36" t="n">
-        <v>440.5400089186511</v>
+        <v>280.6473440501904</v>
       </c>
       <c r="N36" t="n">
-        <v>519.7766803058279</v>
+        <v>359.8840154373673</v>
       </c>
       <c r="O36" t="n">
-        <v>574.5164107992936</v>
+        <v>439.1218909240145</v>
       </c>
       <c r="P36" t="n">
         <v>626.2318909240148</v>
@@ -7037,13 +7037,13 @@
         <v>374.1818181818197</v>
       </c>
       <c r="T36" t="n">
-        <v>374.1818181818197</v>
+        <v>186.2741841713712</v>
       </c>
       <c r="U36" t="n">
-        <v>374.1818181818197</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="V36" t="n">
-        <v>206.0290909090889</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="W36" t="n">
         <v>15.11999999999762</v>
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="C37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="D37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="E37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="F37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="G37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="H37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="I37" t="n">
-        <v>561.0389299975599</v>
+        <v>164.6435278814131</v>
       </c>
       <c r="J37" t="n">
-        <v>748.1489299975602</v>
+        <v>351.7535278814134</v>
       </c>
       <c r="K37" t="n">
-        <v>756.0000000000024</v>
+        <v>359.6045978838556</v>
       </c>
       <c r="L37" t="n">
-        <v>756.0000000000024</v>
+        <v>359.6045978838556</v>
       </c>
       <c r="M37" t="n">
-        <v>756.0000000000024</v>
+        <v>206.0290909090889</v>
       </c>
       <c r="N37" t="n">
-        <v>756.0000000000024</v>
+        <v>206.0290909090889</v>
       </c>
       <c r="O37" t="n">
-        <v>756.0000000000024</v>
+        <v>206.0290909090889</v>
       </c>
       <c r="P37" t="n">
-        <v>756.0000000000024</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="Q37" t="n">
-        <v>565.0909090909111</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="R37" t="n">
-        <v>411.5154021161444</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="S37" t="n">
-        <v>411.5154021161444</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="T37" t="n">
-        <v>420.3601829142935</v>
+        <v>23.96478079814674</v>
       </c>
       <c r="U37" t="n">
-        <v>484.7887683394654</v>
+        <v>88.39336622331862</v>
       </c>
       <c r="V37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="W37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="X37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
       <c r="Y37" t="n">
-        <v>501.4501612254114</v>
+        <v>105.0547591092646</v>
       </c>
     </row>
     <row r="38">
@@ -7141,13 +7141,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="C38" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="D38" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="E38" t="n">
         <v>15.11999999999762</v>
@@ -7156,7 +7156,7 @@
         <v>15.11999999999807</v>
       </c>
       <c r="G38" t="n">
-        <v>15.11999999999887</v>
+        <v>15.11999999999898</v>
       </c>
       <c r="H38" t="n">
         <v>15.11999999999989</v>
@@ -7198,19 +7198,19 @@
         <v>756.0000000000028</v>
       </c>
       <c r="U38" t="n">
-        <v>587.8472727272718</v>
+        <v>587.8472727272714</v>
       </c>
       <c r="V38" t="n">
-        <v>396.9381818181805</v>
+        <v>396.93818181818</v>
       </c>
       <c r="W38" t="n">
-        <v>206.029090909089</v>
+        <v>206.0290909090886</v>
       </c>
       <c r="X38" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="Y38" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
     </row>
     <row r="39">
@@ -7220,31 +7220,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="C39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="D39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="E39" t="n">
         <v>15.11999999999762</v>
       </c>
       <c r="F39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999739</v>
       </c>
       <c r="G39" t="n">
-        <v>15.11999999999875</v>
+        <v>15.11999999999887</v>
       </c>
       <c r="H39" t="n">
-        <v>15.11999999999978</v>
+        <v>15.11999999999983</v>
       </c>
       <c r="I39" t="n">
-        <v>24.60793038452699</v>
+        <v>24.60793038452704</v>
       </c>
       <c r="J39" t="n">
-        <v>211.7179303845274</v>
+        <v>211.7179303845275</v>
       </c>
       <c r="K39" t="n">
         <v>240.0303525528294</v>
@@ -7283,13 +7283,13 @@
         <v>183.2727272727285</v>
       </c>
       <c r="W39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="X39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
       <c r="Y39" t="n">
-        <v>15.11999999999762</v>
+        <v>15.11999999999716</v>
       </c>
     </row>
     <row r="40">
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>206.029090909089</v>
+        <v>183.2727272727285</v>
       </c>
       <c r="C41" t="n">
-        <v>206.029090909089</v>
+        <v>183.2727272727285</v>
       </c>
       <c r="D41" t="n">
         <v>15.11999999999762</v>
@@ -7411,13 +7411,13 @@
         <v>484.3583978877104</v>
       </c>
       <c r="M41" t="n">
-        <v>381.7800000000019</v>
+        <v>484.3583978877104</v>
       </c>
       <c r="N41" t="n">
-        <v>381.7800000000019</v>
+        <v>381.7800000000015</v>
       </c>
       <c r="O41" t="n">
-        <v>568.8900000000024</v>
+        <v>568.8900000000019</v>
       </c>
       <c r="P41" t="n">
         <v>756.0000000000028</v>
@@ -7429,25 +7429,25 @@
         <v>756.0000000000028</v>
       </c>
       <c r="S41" t="n">
+        <v>756.0000000000028</v>
+      </c>
+      <c r="T41" t="n">
         <v>565.0909090909114</v>
       </c>
-      <c r="T41" t="n">
-        <v>396.9381818181805</v>
-      </c>
       <c r="U41" t="n">
-        <v>396.9381818181805</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="V41" t="n">
-        <v>206.029090909089</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="W41" t="n">
-        <v>206.029090909089</v>
+        <v>374.1818181818199</v>
       </c>
       <c r="X41" t="n">
-        <v>206.029090909089</v>
+        <v>374.1818181818199</v>
       </c>
       <c r="Y41" t="n">
-        <v>206.029090909089</v>
+        <v>183.2727272727285</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="C42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="D42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="E42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="F42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="G42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="H42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="I42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="J42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="K42" t="n">
-        <v>584.8572916365329</v>
+        <v>43.43242216829954</v>
       </c>
       <c r="L42" t="n">
-        <v>649.5447893818159</v>
+        <v>108.1199199135826</v>
       </c>
       <c r="M42" t="n">
-        <v>649.5447893818159</v>
+        <v>108.1199199135826</v>
       </c>
       <c r="N42" t="n">
-        <v>649.5447893818159</v>
+        <v>108.1199199135826</v>
       </c>
       <c r="O42" t="n">
-        <v>704.2845198752816</v>
+        <v>162.8596504070483</v>
       </c>
       <c r="P42" t="n">
-        <v>756.0000000000028</v>
+        <v>214.5751305317696</v>
       </c>
       <c r="Q42" t="n">
-        <v>756.0000000000028</v>
+        <v>214.5751305317696</v>
       </c>
       <c r="R42" t="n">
-        <v>756.0000000000028</v>
+        <v>206.029090909089</v>
       </c>
       <c r="S42" t="n">
-        <v>565.0909090909114</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="T42" t="n">
-        <v>565.0909090909114</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="U42" t="n">
-        <v>565.0909090909114</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="V42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="W42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="X42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
       <c r="Y42" t="n">
-        <v>556.5448694682309</v>
+        <v>15.11999999999762</v>
       </c>
     </row>
     <row r="43">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>587.8472727272718</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="C44" t="n">
-        <v>587.8472727272718</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="D44" t="n">
-        <v>587.8472727272718</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="E44" t="n">
+        <v>565.0909090909114</v>
+      </c>
+      <c r="F44" t="n">
         <v>396.9381818181805</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>206.029090909089</v>
-      </c>
-      <c r="G44" t="n">
-        <v>15.11999999999762</v>
       </c>
       <c r="H44" t="n">
         <v>15.11999999999762</v>
@@ -7678,13 +7678,13 @@
         <v>756.0000000000028</v>
       </c>
       <c r="W44" t="n">
-        <v>587.8472727272718</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="X44" t="n">
-        <v>587.8472727272718</v>
+        <v>565.0909090909114</v>
       </c>
       <c r="Y44" t="n">
-        <v>587.8472727272718</v>
+        <v>565.0909090909114</v>
       </c>
     </row>
     <row r="45">
@@ -7976,7 +7976,7 @@
         <v>273.1986502553826</v>
       </c>
       <c r="N2" t="n">
-        <v>158.7651354704114</v>
+        <v>158.7651354704106</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.118443121455272</v>
+        <v>6.118443121455243</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8052,16 +8052,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>259.9787801549791</v>
+        <v>259.9787801549784</v>
       </c>
       <c r="N3" t="n">
-        <v>358.9629581947712</v>
+        <v>358.962958194771</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>170.7621412881606</v>
+        <v>170.7621412881605</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8213,7 +8213,7 @@
         <v>273.1986502553826</v>
       </c>
       <c r="N5" t="n">
-        <v>158.765135470412</v>
+        <v>158.7651354704113</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.118443121455272</v>
+        <v>6.118443121455243</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8283,22 +8283,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K6" t="n">
-        <v>194.4015937693924</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>398.4647782656036</v>
+        <v>175.4647782656031</v>
       </c>
       <c r="N6" t="n">
-        <v>196.8375076029153</v>
+        <v>358.9629581947711</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>84.51400188937569</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>170.7621412881606</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8450,7 +8450,7 @@
         <v>273.1986502553826</v>
       </c>
       <c r="N8" t="n">
-        <v>158.7651354704117</v>
+        <v>158.7651354704116</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.118443121455272</v>
+        <v>6.118443121455243</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8520,22 +8520,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>32.27614317753654</v>
+        <v>194.4015937693924</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>398.4647782656036</v>
+        <v>175.4647782656031</v>
       </c>
       <c r="N9" t="n">
-        <v>358.9629581947713</v>
+        <v>249.0753663147548</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>170.7621412881608</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>47.19865025538263</v>
+        <v>4.164395495155595</v>
       </c>
       <c r="N11" t="n">
-        <v>158.7651354704124</v>
+        <v>23.06022175627344</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8754,19 +8754,19 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>31.22205968042879</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7.092300608738145</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>175.4647782656032</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>135.9629581947709</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>47.19865025538263</v>
+        <v>4.16439549515627</v>
       </c>
       <c r="N14" t="n">
-        <v>158.765135470412</v>
+        <v>201.7993902306392</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.118443121455272</v>
+        <v>0.3191013164943622</v>
       </c>
       <c r="R14" t="n">
         <v>222.4491020973279</v>
@@ -8991,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>13.33337135815792</v>
+        <v>24.22081493539572</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -9158,10 +9158,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>47.19865025538263</v>
+        <v>4.164395495155595</v>
       </c>
       <c r="N17" t="n">
-        <v>22.82432971940519</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.118443121455272</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>222.4491020973279</v>
@@ -9228,22 +9228,22 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>24.22081493539572</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>83.56045896977285</v>
+        <v>157.6590931865832</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>37.64350904256175</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>167.7073429358937</v>
+        <v>166.8710686337333</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -9307,7 +9307,7 @@
         <v>22.34630454117203</v>
       </c>
       <c r="J19" t="n">
-        <v>117.5124126761193</v>
+        <v>117.5124126761192</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>42.83485553941059</v>
+        <v>201.7624338705822</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -9465,13 +9465,13 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>21.22081493539622</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>151.8775105646274</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9480,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>167.7073429358937</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -9632,10 +9632,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>47.19865025538263</v>
+        <v>4.164395495156384</v>
       </c>
       <c r="N23" t="n">
-        <v>76.90220214415017</v>
+        <v>119.9364569043757</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>10.79861250807478</v>
+        <v>10.79861250807473</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -9857,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>7.213964351188466</v>
+        <v>7.213964351188451</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>66.86826862900396</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>82.34145115501623</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>6.118443121455272</v>
       </c>
       <c r="R29" t="n">
         <v>232.4491020973279</v>
@@ -10173,7 +10173,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>17.72758189252907</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -10191,13 +10191,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>61.65610064624589</v>
       </c>
       <c r="P30" t="n">
-        <v>136.7621412881605</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4319583285446527</v>
+        <v>17.27519534353338</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -10346,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>82.34145115501556</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10416,7 +10416,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>97.20596370201257</v>
+        <v>96.65887788230859</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -10431,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>136.7621412881606</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17.27519534353338</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>82.34145115501576</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10656,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>96.65887788230913</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>24.74560100321351</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -11054,10 +11054,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>159.6460363465512</v>
+        <v>261.1986502553826</v>
       </c>
       <c r="N41" t="n">
-        <v>189.7993902306392</v>
+        <v>88.24677632180737</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557428</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22569,19 +22569,19 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>240.9262746937694</v>
+        <v>476.5700562100334</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668237</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809473</v>
+        <v>223.3305807877325</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -22642,7 +22642,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>51.22211317215825</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -22703,10 +22703,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12.08551304189393</v>
+        <v>12.0855130418939</v>
       </c>
       <c r="N4" t="n">
-        <v>65.21996051758627</v>
+        <v>65.21996051758624</v>
       </c>
       <c r="O4" t="n">
         <v>142.5696296527852</v>
@@ -22715,10 +22715,10 @@
         <v>203.698126836474</v>
       </c>
       <c r="Q4" t="n">
-        <v>254.439752084589</v>
+        <v>254.4397520845889</v>
       </c>
       <c r="R4" t="n">
-        <v>295.4666525713148</v>
+        <v>295.4666525713147</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22752,16 +22752,16 @@
         <v>81.99931295557428</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299369</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984956</v>
       </c>
       <c r="E5" t="n">
-        <v>4.36328960686842</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011628</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -22770,7 +22770,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>90.56694862740821</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22800,19 +22800,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>59.67068036513674</v>
+        <v>59.67068036513673</v>
       </c>
       <c r="T5" t="n">
-        <v>177.995040742577</v>
+        <v>179.9179535878601</v>
       </c>
       <c r="U5" t="n">
-        <v>26.09779906117285</v>
+        <v>241.2826256855901</v>
       </c>
       <c r="V5" t="n">
-        <v>6.851024166823265</v>
+        <v>6.851024166823379</v>
       </c>
       <c r="W5" t="n">
-        <v>15.37347598094692</v>
+        <v>238.3734759809473</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -22831,7 +22831,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -22849,7 +22849,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.336545850072383</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -22876,22 +22876,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>95.99168408483189</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>51.22211317215825</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.028557670343778</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1560201375450109</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982829</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -22940,10 +22940,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>12.0855130418939</v>
       </c>
       <c r="N7" t="n">
-        <v>65.21996051758627</v>
+        <v>65.21996051758624</v>
       </c>
       <c r="O7" t="n">
         <v>142.5696296527852</v>
@@ -22952,10 +22952,10 @@
         <v>203.698126836474</v>
       </c>
       <c r="Q7" t="n">
-        <v>267.8552664255978</v>
+        <v>254.4397520845889</v>
       </c>
       <c r="R7" t="n">
-        <v>295.4666525713148</v>
+        <v>295.4666525713147</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23037,10 +23037,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>59.67068036513696</v>
       </c>
       <c r="T8" t="n">
-        <v>179.9179535878604</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>26.09779906117308</v>
@@ -23049,13 +23049,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>74.89658238025368</v>
       </c>
       <c r="X8" t="n">
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -23071,7 +23071,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>118.7045793067524</v>
+        <v>124.9376868977022</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23128,10 +23128,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>31.33947139041735</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -23177,10 +23177,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>12.08551304189416</v>
+        <v>12.08551304189413</v>
       </c>
       <c r="N10" t="n">
-        <v>65.2199605175865</v>
+        <v>65.21996051758647</v>
       </c>
       <c r="O10" t="n">
         <v>142.5696296527854</v>
@@ -23189,7 +23189,7 @@
         <v>203.6981268364742</v>
       </c>
       <c r="Q10" t="n">
-        <v>254.4397520845893</v>
+        <v>254.4397520845892</v>
       </c>
       <c r="R10" t="n">
         <v>295.466652571315</v>
@@ -23229,19 +23229,19 @@
         <v>223.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>18.58737841210507</v>
+        <v>184.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>178.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>178.8896287080133</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>176.2136536940514</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>166.2000506633264</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23277,19 +23277,19 @@
         <v>233.670680365137</v>
       </c>
       <c r="T11" t="n">
-        <v>353.9179535878604</v>
+        <v>130.91795358786</v>
       </c>
       <c r="U11" t="n">
         <v>423.0977990611735</v>
       </c>
       <c r="V11" t="n">
-        <v>403.8510241668239</v>
+        <v>180.8510241668235</v>
       </c>
       <c r="W11" t="n">
-        <v>412.3734759809475</v>
+        <v>189.3734759809471</v>
       </c>
       <c r="X11" t="n">
-        <v>366.2818334606677</v>
+        <v>169.8634334606645</v>
       </c>
       <c r="Y11" t="n">
         <v>285.3174326828064</v>
@@ -23320,7 +23320,7 @@
         <v>98.9135736108764</v>
       </c>
       <c r="H12" t="n">
-        <v>98.19103058264754</v>
+        <v>28.95720839053315</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -23359,13 +23359,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>174.1560201375452</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>151.4939677716886</v>
+        <v>188.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>206.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>193.8627394453875</v>
@@ -23417,13 +23417,13 @@
         <v>186.0855130418942</v>
       </c>
       <c r="N13" t="n">
-        <v>35.5337152850918</v>
+        <v>16.21996051758612</v>
       </c>
       <c r="O13" t="n">
-        <v>93.56962965278501</v>
+        <v>316.5696296527854</v>
       </c>
       <c r="P13" t="n">
-        <v>377.6981268364742</v>
+        <v>174.0118816039795</v>
       </c>
       <c r="Q13" t="n">
         <v>441.855266425598</v>
@@ -23460,25 +23460,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.99931295557411</v>
+        <v>255.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>223.4745782429939</v>
+        <v>0.4745782429935161</v>
       </c>
       <c r="D14" t="n">
         <v>184.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>178.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>114.04817200893</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>166.2000506633264</v>
+        <v>101.8849330653874</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23542,10 +23542,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>135.0999124455193</v>
+        <v>1.422646899731177</v>
       </c>
       <c r="D15" t="n">
-        <v>86.45145193456383</v>
+        <v>121.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>116.6720972219126</v>
@@ -23557,7 +23557,7 @@
         <v>98.9135736108764</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>98.19103058264754</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23621,19 +23621,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>46.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>59.53621805555548</v>
+        <v>9.683531129647804</v>
       </c>
       <c r="E16" t="n">
-        <v>36.82610044228871</v>
+        <v>54.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>48.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>18.35141382513659</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>94.59785766597588</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23684,10 +23684,10 @@
         <v>0.372809838709685</v>
       </c>
       <c r="X16" t="n">
-        <v>21.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>61.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23697,25 +23697,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.999312955574</v>
+        <v>32.99931295557411</v>
       </c>
       <c r="C17" t="n">
-        <v>223.4745782429939</v>
+        <v>0.4745782429935161</v>
       </c>
       <c r="D17" t="n">
-        <v>65.37372471805413</v>
+        <v>184.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>178.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>178.8896287080136</v>
       </c>
       <c r="G17" t="n">
         <v>176.2136536940514</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>166.2000506633264</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23751,13 +23751,13 @@
         <v>233.670680365137</v>
       </c>
       <c r="T17" t="n">
-        <v>353.9179535878604</v>
+        <v>130.91795358786</v>
       </c>
       <c r="U17" t="n">
         <v>423.0977990611735</v>
       </c>
       <c r="V17" t="n">
-        <v>403.8510241668239</v>
+        <v>207.4326241668203</v>
       </c>
       <c r="W17" t="n">
         <v>412.3734759809475</v>
@@ -23776,10 +23776,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>135.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>121.9376868977026</v>
@@ -23794,7 +23794,7 @@
         <v>98.9135736108764</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>98.19103058264979</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23827,13 +23827,13 @@
         <v>269.9916840848321</v>
       </c>
       <c r="S18" t="n">
-        <v>2.222113172157975</v>
+        <v>2.222113172158089</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>134.9198602814384</v>
+        <v>60.18547389959893</v>
       </c>
       <c r="V18" t="n">
         <v>188.5106671915202</v>
@@ -23855,19 +23855,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>46.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>59.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>54.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>48.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>18.35141382513659</v>
@@ -23885,13 +23885,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>76.99712547537533</v>
+        <v>94.59785766597588</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>186.0855130418942</v>
       </c>
       <c r="N19" t="n">
-        <v>16.219960517586</v>
+        <v>239.2199605175865</v>
       </c>
       <c r="O19" t="n">
         <v>316.5696296527854</v>
@@ -23906,7 +23906,7 @@
         <v>469.466652571315</v>
       </c>
       <c r="S19" t="n">
-        <v>124.3058075717079</v>
+        <v>29.8239410340525</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>21.44364543010755</v>
       </c>
       <c r="Y19" t="n">
-        <v>61.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59.58091295557031</v>
+        <v>32.999312955574</v>
       </c>
       <c r="C20" t="n">
         <v>223.4745782429939</v>
@@ -23943,13 +23943,13 @@
         <v>184.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>178.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>178.8896287080119</v>
+        <v>114.0481720089298</v>
       </c>
       <c r="G20" t="n">
-        <v>176.2136536940541</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>166.2000506633264</v>
@@ -23994,10 +23994,10 @@
         <v>200.097799061173</v>
       </c>
       <c r="V20" t="n">
-        <v>180.8510241668234</v>
+        <v>403.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>189.373475980947</v>
+        <v>412.3734759809475</v>
       </c>
       <c r="X20" t="n">
         <v>366.2818334606677</v>
@@ -24013,16 +24013,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>158.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.422646899732484</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>121.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>116.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>113.6362423378769</v>
@@ -24070,13 +24070,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>174.1560201375452</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>188.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>113.6929971453045</v>
+        <v>206.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>193.8627394453875</v>
@@ -24104,10 +24104,10 @@
         <v>54.98090483695654</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>48.38285596774193</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>18.35141382513659</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -24122,13 +24122,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>76.99712547537533</v>
       </c>
       <c r="M22" t="n">
-        <v>45.0372028399612</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>239.2199605175865</v>
+        <v>16.219960517586</v>
       </c>
       <c r="O22" t="n">
         <v>316.5696296527854</v>
@@ -24143,7 +24143,7 @@
         <v>469.466652571315</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>124.3058075717079</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>178.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>176.2136536940543</v>
+        <v>176.2136536940538</v>
       </c>
       <c r="H23" t="n">
         <v>166.2000506633264</v>
@@ -24256,16 +24256,16 @@
         <v>135.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>121.9376868977026</v>
+        <v>59.24757689396761</v>
       </c>
       <c r="E24" t="n">
-        <v>51.34273803252709</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>98.9135736108764</v>
       </c>
       <c r="H24" t="n">
         <v>98.19103058264754</v>
@@ -24310,7 +24310,7 @@
         <v>174.1560201375452</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>188.5106671915202</v>
       </c>
       <c r="W24" t="n">
         <v>206.3731429098285</v>
@@ -24319,7 +24319,7 @@
         <v>193.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>173.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24335,13 +24335,13 @@
         <v>46.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>59.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>54.98090483695654</v>
       </c>
       <c r="F25" t="n">
-        <v>4.856692436839026</v>
+        <v>14.64537711603491</v>
       </c>
       <c r="G25" t="n">
         <v>18.35141382513659</v>
@@ -24380,7 +24380,7 @@
         <v>469.466652571315</v>
       </c>
       <c r="S25" t="n">
-        <v>124.3058075717079</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24408,22 +24408,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>88.99931295557451</v>
+        <v>277.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>56.47457824299391</v>
       </c>
       <c r="D26" t="n">
-        <v>39.86795573984779</v>
+        <v>206.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>200.3632896068686</v>
+        <v>33.89208960686665</v>
       </c>
       <c r="F26" t="n">
         <v>200.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>9.213653694051374</v>
+        <v>198.2136536940514</v>
       </c>
       <c r="H26" t="n">
         <v>188.2000506633264</v>
@@ -24462,7 +24462,7 @@
         <v>255.670680365137</v>
       </c>
       <c r="T26" t="n">
-        <v>375.9179535878604</v>
+        <v>186.9179535878604</v>
       </c>
       <c r="U26" t="n">
         <v>445.0977990611735</v>
@@ -24471,7 +24471,7 @@
         <v>425.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>434.3734759809475</v>
+        <v>245.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>388.2818334606677</v>
@@ -24487,22 +24487,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>106.3530699097138</v>
+        <v>180.5565566463266</v>
       </c>
       <c r="C27" t="n">
         <v>157.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>143.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>138.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>135.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>120.9135736108764</v>
       </c>
       <c r="H27" t="n">
         <v>120.1910305826475</v>
@@ -24544,13 +24544,13 @@
         <v>198.028557670344</v>
       </c>
       <c r="U27" t="n">
-        <v>196.1560201375452</v>
+        <v>113.8028048961506</v>
       </c>
       <c r="V27" t="n">
-        <v>210.5106671915202</v>
+        <v>21.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>228.3731429098285</v>
+        <v>39.37314290982852</v>
       </c>
       <c r="X27" t="n">
         <v>215.8627394453875</v>
@@ -24581,7 +24581,7 @@
         <v>70.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>40.35141382513659</v>
+        <v>10.28776686442586</v>
       </c>
       <c r="H28" t="n">
         <v>18.61453593768419</v>
@@ -24617,7 +24617,7 @@
         <v>491.466652571315</v>
       </c>
       <c r="S28" t="n">
-        <v>141.5722286146214</v>
+        <v>146.3058075717079</v>
       </c>
       <c r="T28" t="n">
         <v>3.06587798166755</v>
@@ -24645,25 +24645,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>76.99931295557437</v>
+        <v>265.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>233.4745782429939</v>
+        <v>67.00337824299154</v>
       </c>
       <c r="D29" t="n">
-        <v>5.339155739849645</v>
+        <v>194.3391557398512</v>
       </c>
       <c r="E29" t="n">
-        <v>21.78171831487842</v>
+        <v>188.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>188.8896287080119</v>
       </c>
       <c r="G29" t="n">
         <v>186.2136536940514</v>
       </c>
       <c r="H29" t="n">
-        <v>176.2000506633273</v>
+        <v>176.2000506633264</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,7 +24699,7 @@
         <v>243.670680365137</v>
       </c>
       <c r="T29" t="n">
-        <v>363.9179535878604</v>
+        <v>174.9179535878602</v>
       </c>
       <c r="U29" t="n">
         <v>433.0977990611735</v>
@@ -24708,13 +24708,13 @@
         <v>413.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>422.3734759809475</v>
+        <v>233.3734759809474</v>
       </c>
       <c r="X29" t="n">
         <v>376.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>295.3174326828064</v>
+        <v>106.3174326828062</v>
       </c>
     </row>
     <row r="30">
@@ -24724,25 +24724,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>147.1852690918436</v>
+        <v>168.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>145.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>131.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>126.6720972219139</v>
+        <v>3.028170142435755</v>
       </c>
       <c r="F30" t="n">
-        <v>123.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>108.9135736108764</v>
       </c>
       <c r="H30" t="n">
-        <v>108.1910305826475</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -24784,7 +24784,7 @@
         <v>184.1560201375452</v>
       </c>
       <c r="V30" t="n">
-        <v>9.510667191520014</v>
+        <v>198.5106671915202</v>
       </c>
       <c r="W30" t="n">
         <v>216.3731429098285</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>104.5978576659759</v>
       </c>
       <c r="M31" t="n">
         <v>7.085513041894018</v>
@@ -24851,10 +24851,10 @@
         <v>451.855266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>479.466652571315</v>
+        <v>327.426900666296</v>
       </c>
       <c r="S31" t="n">
-        <v>86.86391333266477</v>
+        <v>134.3058075717079</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24885,10 +24885,10 @@
         <v>265.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>67.003378242991</v>
+        <v>233.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>194.3391557398516</v>
+        <v>194.3391557398498</v>
       </c>
       <c r="E32" t="n">
         <v>188.3632896068686</v>
@@ -24897,7 +24897,7 @@
         <v>188.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>186.2136536940514</v>
+        <v>186.2136536940528</v>
       </c>
       <c r="H32" t="n">
         <v>176.2000506633264</v>
@@ -24936,22 +24936,22 @@
         <v>243.670680365137</v>
       </c>
       <c r="T32" t="n">
-        <v>174.9179535878601</v>
+        <v>363.9179535878604</v>
       </c>
       <c r="U32" t="n">
-        <v>433.0977990611735</v>
+        <v>244.0977990611732</v>
       </c>
       <c r="V32" t="n">
-        <v>413.8510241668239</v>
+        <v>224.8510241668236</v>
       </c>
       <c r="W32" t="n">
         <v>233.3734759809473</v>
       </c>
       <c r="X32" t="n">
-        <v>376.2818334606677</v>
+        <v>209.8106334606648</v>
       </c>
       <c r="Y32" t="n">
-        <v>106.3174326828061</v>
+        <v>295.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -24961,7 +24961,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>47.9484844508854</v>
+        <v>168.5565566463266</v>
       </c>
       <c r="C33" t="n">
         <v>145.0999124455193</v>
@@ -24970,16 +24970,16 @@
         <v>131.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>126.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>123.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>108.9135736108764</v>
+        <v>108.9135736108782</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>108.1910305826475</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -25009,7 +25009,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>90.99168408483186</v>
+        <v>279.9916840848321</v>
       </c>
       <c r="S33" t="n">
         <v>46.22211317215823</v>
@@ -25021,13 +25021,13 @@
         <v>184.1560201375452</v>
       </c>
       <c r="V33" t="n">
-        <v>198.5106671915202</v>
+        <v>9.5106671915199</v>
       </c>
       <c r="W33" t="n">
-        <v>216.3731429098285</v>
+        <v>27.37314290982826</v>
       </c>
       <c r="X33" t="n">
-        <v>203.8627394453875</v>
+        <v>37.39153944538464</v>
       </c>
       <c r="Y33" t="n">
         <v>183.3913927661343</v>
@@ -25082,10 +25082,10 @@
         <v>326.5696296527854</v>
       </c>
       <c r="P34" t="n">
-        <v>387.6981268364742</v>
+        <v>235.6583749314552</v>
       </c>
       <c r="Q34" t="n">
-        <v>299.815514520579</v>
+        <v>451.855266425598</v>
       </c>
       <c r="R34" t="n">
         <v>479.466652571315</v>
@@ -25122,10 +25122,10 @@
         <v>265.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>233.4745782429939</v>
+        <v>44.47457824299354</v>
       </c>
       <c r="D35" t="n">
-        <v>194.3391557398498</v>
+        <v>194.3391557398519</v>
       </c>
       <c r="E35" t="n">
         <v>188.3632896068686</v>
@@ -25170,25 +25170,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>243.670680365137</v>
+        <v>54.6706803651366</v>
       </c>
       <c r="T35" t="n">
-        <v>363.9179535878604</v>
+        <v>197.4467535878569</v>
       </c>
       <c r="U35" t="n">
-        <v>266.626599061172</v>
+        <v>433.0977990611735</v>
       </c>
       <c r="V35" t="n">
-        <v>224.8510241668235</v>
+        <v>413.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>233.3734759809472</v>
+        <v>422.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>187.2818334606673</v>
+        <v>376.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>295.3174326828064</v>
+        <v>106.317432682806</v>
       </c>
     </row>
     <row r="36">
@@ -25216,7 +25216,7 @@
         <v>108.9135736108764</v>
       </c>
       <c r="H36" t="n">
-        <v>108.19103058265</v>
+        <v>108.1910305826499</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -25252,16 +25252,16 @@
         <v>46.22211317215812</v>
       </c>
       <c r="T36" t="n">
-        <v>186.028557670344</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>184.1560201375452</v>
+        <v>14.71337780788537</v>
       </c>
       <c r="V36" t="n">
-        <v>32.03946719151668</v>
+        <v>198.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>27.37314290982815</v>
+        <v>216.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>203.8627394453875</v>
@@ -25310,7 +25310,7 @@
         <v>104.5978576659759</v>
       </c>
       <c r="M37" t="n">
-        <v>196.0855130418942</v>
+        <v>44.04576113687514</v>
       </c>
       <c r="N37" t="n">
         <v>249.2199605175865</v>
@@ -25319,13 +25319,13 @@
         <v>326.5696296527854</v>
       </c>
       <c r="P37" t="n">
-        <v>387.6981268364742</v>
+        <v>198.6981268364738</v>
       </c>
       <c r="Q37" t="n">
-        <v>262.8552664255976</v>
+        <v>451.855266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>327.426900666296</v>
+        <v>479.466652571315</v>
       </c>
       <c r="S37" t="n">
         <v>134.3058075717079</v>
@@ -25368,13 +25368,13 @@
         <v>188.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>188.8896287080119</v>
+        <v>188.8896287080128</v>
       </c>
       <c r="G38" t="n">
-        <v>186.2136536940514</v>
+        <v>186.2136536940523</v>
       </c>
       <c r="H38" t="n">
-        <v>176.2000506633274</v>
+        <v>176.2000506633273</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>363.9179535878604</v>
       </c>
       <c r="U38" t="n">
-        <v>266.6265990611698</v>
+        <v>266.6265990611694</v>
       </c>
       <c r="V38" t="n">
         <v>224.8510241668234</v>
@@ -25450,10 +25450,10 @@
         <v>123.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>108.9135736108775</v>
+        <v>108.9135736108781</v>
       </c>
       <c r="H39" t="n">
-        <v>108.1910305826486</v>
+        <v>108.1910305826485</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -25498,7 +25498,7 @@
         <v>9.510667191519673</v>
       </c>
       <c r="W39" t="n">
-        <v>49.90194290982492</v>
+        <v>49.90194290982447</v>
       </c>
       <c r="X39" t="n">
         <v>203.8627394453875</v>
@@ -25599,7 +25599,7 @@
         <v>437.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>209.3391557398493</v>
+        <v>231.8679557398462</v>
       </c>
       <c r="E41" t="n">
         <v>392.3632896068686</v>
@@ -25644,25 +25644,25 @@
         <v>141.9079857629678</v>
       </c>
       <c r="S41" t="n">
-        <v>258.6706803651365</v>
+        <v>447.6706803651369</v>
       </c>
       <c r="T41" t="n">
-        <v>401.4467535878567</v>
+        <v>378.9179535878599</v>
       </c>
       <c r="U41" t="n">
         <v>637.0977990611735</v>
       </c>
       <c r="V41" t="n">
-        <v>428.8510241668234</v>
+        <v>617.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>626.3734759809475</v>
+        <v>437.3734759809471</v>
       </c>
       <c r="X41" t="n">
         <v>580.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>499.3174326828064</v>
+        <v>310.3174326828059</v>
       </c>
     </row>
     <row r="42">
@@ -25720,7 +25720,7 @@
         <v>55.64590659991353</v>
       </c>
       <c r="R42" t="n">
-        <v>483.9916840848321</v>
+        <v>475.5311048583784</v>
       </c>
       <c r="S42" t="n">
         <v>250.222113172158</v>
@@ -25732,7 +25732,7 @@
         <v>388.1560201375452</v>
       </c>
       <c r="V42" t="n">
-        <v>394.0500879650664</v>
+        <v>402.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>420.3731429098285</v>
@@ -25839,16 +25839,16 @@
         <v>410.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>215.3632896068682</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>215.8896287080114</v>
+        <v>238.4184287080082</v>
       </c>
       <c r="G44" t="n">
         <v>213.2136536940509</v>
       </c>
       <c r="H44" t="n">
-        <v>392.2000506633264</v>
+        <v>203.2000506633259</v>
       </c>
       <c r="I44" t="n">
         <v>90.56694862740821</v>
@@ -25893,7 +25893,7 @@
         <v>629.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>471.9022759809438</v>
+        <v>449.3734759809471</v>
       </c>
       <c r="X44" t="n">
         <v>592.2818334606677</v>
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1914490.47941402</v>
+        <v>1914490.479414019</v>
       </c>
     </row>
     <row r="4">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4837618.047428055</v>
+        <v>4837618.047428057</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5537087.334112578</v>
+        <v>5537087.334112579</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6236556.620797099</v>
+        <v>6236556.6207971</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6852002.377133071</v>
+        <v>6852002.377133072</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7532533.662501114</v>
+        <v>7532533.662501115</v>
       </c>
     </row>
     <row r="12">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9846217.835435102</v>
+        <v>9846217.8354351</v>
       </c>
     </row>
     <row r="16">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1132955.164449207</v>
+        <v>1132955.164449208</v>
       </c>
       <c r="C2" t="n">
         <v>1132955.164449208</v>
@@ -26278,34 +26278,34 @@
         <v>1132955.164449208</v>
       </c>
       <c r="E2" t="n">
-        <v>879977.4896998905</v>
+        <v>879977.48969989</v>
       </c>
       <c r="F2" t="n">
+        <v>879977.4896998901</v>
+      </c>
+      <c r="G2" t="n">
         <v>879977.48969989</v>
       </c>
-      <c r="G2" t="n">
-        <v>879977.4896998901</v>
-      </c>
       <c r="H2" t="n">
-        <v>879977.48969989</v>
+        <v>879977.4896998898</v>
       </c>
       <c r="I2" t="n">
-        <v>879977.48969989</v>
+        <v>879977.4896998903</v>
       </c>
       <c r="J2" t="n">
-        <v>796810.473030207</v>
+        <v>796810.4730302069</v>
       </c>
       <c r="K2" t="n">
+        <v>841079.062175085</v>
+      </c>
+      <c r="L2" t="n">
+        <v>841079.0621750845</v>
+      </c>
+      <c r="M2" t="n">
+        <v>841079.0621750851</v>
+      </c>
+      <c r="N2" t="n">
         <v>841079.0621750847</v>
-      </c>
-      <c r="L2" t="n">
-        <v>841079.0621750847</v>
-      </c>
-      <c r="M2" t="n">
-        <v>841079.0621750848</v>
-      </c>
-      <c r="N2" t="n">
-        <v>841079.0621750851</v>
       </c>
       <c r="O2" t="n">
         <v>329996.6859108119</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>580398.6357732952</v>
+        <v>580293.4448477388</v>
       </c>
       <c r="C4" t="n">
-        <v>578525.9910118405</v>
+        <v>578420.8000862841</v>
       </c>
       <c r="D4" t="n">
-        <v>576650.8058908844</v>
+        <v>576545.6149653282</v>
       </c>
       <c r="E4" t="n">
-        <v>396272.9883859822</v>
+        <v>396238.153173654</v>
       </c>
       <c r="F4" t="n">
-        <v>394811.3996060441</v>
+        <v>394776.5643937159</v>
       </c>
       <c r="G4" t="n">
-        <v>393347.7938884268</v>
+        <v>393312.9586760985</v>
       </c>
       <c r="H4" t="n">
-        <v>391882.1567695926</v>
+        <v>391847.3215572644</v>
       </c>
       <c r="I4" t="n">
-        <v>390414.4735975522</v>
+        <v>390379.6383852239</v>
       </c>
       <c r="J4" t="n">
-        <v>336822.7123440572</v>
+        <v>336804.4991683112</v>
       </c>
       <c r="K4" t="n">
-        <v>365995.09139939</v>
+        <v>365965.7625527025</v>
       </c>
       <c r="L4" t="n">
-        <v>364586.6047792399</v>
+        <v>364557.2759325524</v>
       </c>
       <c r="M4" t="n">
-        <v>363176.1050500237</v>
+        <v>363146.7762033362</v>
       </c>
       <c r="N4" t="n">
-        <v>361763.5772567422</v>
+        <v>361734.2484100548</v>
       </c>
       <c r="O4" t="n">
-        <v>95670.27480104459</v>
+        <v>95598.52062235156</v>
       </c>
       <c r="P4" t="n">
-        <v>80413.79310816526</v>
+        <v>80339.25143501355</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44103.32867591229</v>
+        <v>44208.51960146888</v>
       </c>
       <c r="C6" t="n">
-        <v>498871.9734373672</v>
+        <v>498977.1643629239</v>
       </c>
       <c r="D6" t="n">
-        <v>500747.1585583236</v>
+        <v>500852.3494838795</v>
       </c>
       <c r="E6" t="n">
-        <v>261975.3073139082</v>
+        <v>262010.142526236</v>
       </c>
       <c r="F6" t="n">
-        <v>444236.8960938459</v>
+        <v>444271.7313061742</v>
       </c>
       <c r="G6" t="n">
-        <v>445700.5018114633</v>
+        <v>445735.3370237915</v>
       </c>
       <c r="H6" t="n">
-        <v>447166.1389302974</v>
+        <v>447200.9741426253</v>
       </c>
       <c r="I6" t="n">
-        <v>448633.8221023378</v>
+        <v>448668.6573146663</v>
       </c>
       <c r="J6" t="n">
-        <v>193247.2846861498</v>
+        <v>193265.4978618956</v>
       </c>
       <c r="K6" t="n">
-        <v>427462.6667756948</v>
+        <v>427491.9956223825</v>
       </c>
       <c r="L6" t="n">
-        <v>438471.1533958449</v>
+        <v>438500.4822425321</v>
       </c>
       <c r="M6" t="n">
-        <v>439881.6531250611</v>
+        <v>439910.9819717489</v>
       </c>
       <c r="N6" t="n">
-        <v>441294.1809183428</v>
+        <v>441323.5097650299</v>
       </c>
       <c r="O6" t="n">
-        <v>213455.1831097673</v>
+        <v>213526.9372884603</v>
       </c>
       <c r="P6" t="n">
-        <v>199927.6128026466</v>
+        <v>200002.1544757983</v>
       </c>
     </row>
   </sheetData>
@@ -27445,7 +27445,7 @@
         <v>400.0000000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>290.378832163217</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="G2" t="n">
         <v>400.0000000000002</v>
@@ -27454,7 +27454,7 @@
         <v>392.2000506633264</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>90.56694862740821</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27490,7 +27490,7 @@
         <v>400.0000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>400.0000000000002</v>
+        <v>172.52774285114</v>
       </c>
       <c r="V2" t="n">
         <v>400.0000000000002</v>
@@ -27521,7 +27521,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219145</v>
+        <v>119.6720972219125</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27533,7 +27533,7 @@
         <v>324.1910305826476</v>
       </c>
       <c r="I3" t="n">
-        <v>188.6886500422919</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>67.64590659991353</v>
+        <v>67.6459065999135</v>
       </c>
       <c r="R3" t="n">
-        <v>272.9916840848318</v>
+        <v>272.9916840848319</v>
       </c>
       <c r="S3" t="n">
         <v>400.0000000000002</v>
@@ -27569,16 +27569,16 @@
         <v>400.0000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>177.1560201375449</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="V3" t="n">
-        <v>191.5106671915199</v>
+        <v>400.0000000000002</v>
       </c>
       <c r="W3" t="n">
         <v>400.0000000000002</v>
       </c>
       <c r="X3" t="n">
-        <v>257.8460400255565</v>
+        <v>289.4234905690734</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27682,16 +27682,16 @@
         <v>400.0000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>400.0000000000002</v>
+        <v>393.3140891570908</v>
       </c>
       <c r="G5" t="n">
-        <v>400.0000000000002</v>
+        <v>179.2136536940511</v>
       </c>
       <c r="H5" t="n">
         <v>392.2000506633264</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>90.56694862740821</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>153.9079857629678</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>400.0000000000002</v>
@@ -27752,10 +27752,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>300.9797186417792</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,10 +27764,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>101.913573610876</v>
+        <v>324.9135736108764</v>
       </c>
       <c r="H6" t="n">
-        <v>105.6354019663853</v>
+        <v>101.1910305826473</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>67.64590659991353</v>
+        <v>67.6459065999135</v>
       </c>
       <c r="R6" t="n">
         <v>400.0000000000002</v>
@@ -27812,10 +27812,10 @@
         <v>400.0000000000002</v>
       </c>
       <c r="W6" t="n">
+        <v>209.3731429098282</v>
+      </c>
+      <c r="X6" t="n">
         <v>400.0000000000002</v>
-      </c>
-      <c r="X6" t="n">
-        <v>196.8627394453871</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27879,7 +27879,7 @@
         <v>400.0000000000002</v>
       </c>
       <c r="S7" t="n">
-        <v>348.975806272593</v>
+        <v>350.3058075717079</v>
       </c>
       <c r="T7" t="n">
         <v>207.0658779816675</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>318.5243170489939</v>
+        <v>392.2000506633264</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27961,7 +27961,7 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>356.9179535878599</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27992,7 +27992,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>6.233107590949818</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28004,10 +28004,10 @@
         <v>324.9135736108764</v>
       </c>
       <c r="H9" t="n">
-        <v>101.1910305826472</v>
+        <v>103.0499010006621</v>
       </c>
       <c r="I9" t="n">
-        <v>188.6886500422919</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>263.7638239776624</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28180,7 +28180,7 @@
         <v>226</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>178.7391684743658</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28247,25 +28247,25 @@
         <v>226</v>
       </c>
       <c r="J12" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>157.6590931865832</v>
       </c>
       <c r="M12" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>153.6860729427027</v>
+        <v>167.7073429358936</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>170.7621412881608</v>
       </c>
       <c r="Q12" t="n">
         <v>226</v>
@@ -28426,7 +28426,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.79934180496091</v>
       </c>
       <c r="R14" t="n">
         <v>226</v>
@@ -28484,13 +28484,13 @@
         <v>226</v>
       </c>
       <c r="J15" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>194.4015937693924</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>18.17620380328775</v>
       </c>
       <c r="M15" t="n">
         <v>226</v>
@@ -28499,7 +28499,7 @@
         <v>226</v>
       </c>
       <c r="O15" t="n">
-        <v>165.1725840858098</v>
+        <v>167.7073429358936</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -28639,7 +28639,7 @@
         <v>226</v>
       </c>
       <c r="I17" t="n">
-        <v>211.2139643511872</v>
+        <v>211.2139643511885</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28654,7 +28654,7 @@
         <v>226</v>
       </c>
       <c r="N17" t="n">
-        <v>135.9408057510082</v>
+        <v>201.7993902306392</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -28663,7 +28663,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6.118443121455272</v>
       </c>
       <c r="R17" t="n">
         <v>226</v>
@@ -28721,7 +28721,7 @@
         <v>226</v>
       </c>
       <c r="J18" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -28733,10 +28733,10 @@
         <v>226</v>
       </c>
       <c r="N18" t="n">
-        <v>135.9629581947709</v>
+        <v>226</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.836274302160311</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -28812,7 +28812,7 @@
         <v>226</v>
       </c>
       <c r="N19" t="n">
-        <v>225.9999999999999</v>
+        <v>226</v>
       </c>
       <c r="O19" t="n">
         <v>226</v>
@@ -28876,7 +28876,7 @@
         <v>226</v>
       </c>
       <c r="I20" t="n">
-        <v>211.2139643511885</v>
+        <v>211.2139643511876</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28888,10 +28888,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>226</v>
+        <v>28.40196162457395</v>
       </c>
       <c r="N20" t="n">
-        <v>163.1289301863842</v>
+        <v>201.7993902306392</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -28976,10 +28976,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>157.2851405085721</v>
       </c>
       <c r="Q21" t="n">
-        <v>84.92110194344691</v>
+        <v>226</v>
       </c>
       <c r="R21" t="n">
         <v>226</v>
@@ -29049,7 +29049,7 @@
         <v>226</v>
       </c>
       <c r="N22" t="n">
-        <v>226</v>
+        <v>225.9999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>226</v>
@@ -29128,7 +29128,7 @@
         <v>226</v>
       </c>
       <c r="N23" t="n">
-        <v>81.86293332626336</v>
+        <v>81.86293332626356</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -29365,7 +29365,7 @@
         <v>204</v>
       </c>
       <c r="N26" t="n">
-        <v>169.4454265771882</v>
+        <v>169.4454265771881</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29432,19 +29432,19 @@
         <v>204</v>
       </c>
       <c r="J27" t="n">
-        <v>91.4289639775338</v>
+        <v>24.22081493539572</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>123.6590931865828</v>
       </c>
       <c r="M27" t="n">
         <v>204</v>
       </c>
       <c r="N27" t="n">
-        <v>204</v>
+        <v>135.9629581947709</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>204</v>
+        <v>200.957208423284</v>
       </c>
       <c r="R27" t="n">
         <v>204</v>
@@ -29508,7 +29508,7 @@
         <v>204</v>
       </c>
       <c r="I28" t="n">
-        <v>178.1556290137493</v>
+        <v>204</v>
       </c>
       <c r="J28" t="n">
         <v>120.5124126761188</v>
@@ -29599,10 +29599,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>104.7777677175448</v>
+        <v>216</v>
       </c>
       <c r="N29" t="n">
-        <v>201.7993902306392</v>
+        <v>75.10397542217136</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -29611,7 +29611,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.118443121455272</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>216</v>
@@ -29678,7 +29678,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>175.4647782656032</v>
+        <v>216</v>
       </c>
       <c r="N30" t="n">
         <v>216</v>
@@ -29772,7 +29772,7 @@
         <v>216</v>
       </c>
       <c r="R31" t="n">
-        <v>216</v>
+        <v>215.9999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>216</v>
@@ -29836,10 +29836,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>171.6460363465485</v>
+        <v>171.6460363465487</v>
       </c>
       <c r="N32" t="n">
-        <v>201.7993902306392</v>
+        <v>119.4579390756237</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -29906,7 +29906,7 @@
         <v>216</v>
       </c>
       <c r="J33" t="n">
-        <v>24.22081493539572</v>
+        <v>213.220814935396</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29921,7 +29921,7 @@
         <v>216</v>
       </c>
       <c r="O33" t="n">
-        <v>34.41557754860227</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -30061,7 +30061,7 @@
         <v>216</v>
       </c>
       <c r="I35" t="n">
-        <v>211.2139643511875</v>
+        <v>90.56694862740821</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30073,10 +30073,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>216</v>
+        <v>171.6460363465488</v>
       </c>
       <c r="N35" t="n">
-        <v>75.10397542217316</v>
+        <v>201.7993902306392</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -30143,7 +30143,7 @@
         <v>216</v>
       </c>
       <c r="J36" t="n">
-        <v>213.2208149353961</v>
+        <v>148.3719505263309</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>136.7621412881608</v>
       </c>
       <c r="Q36" t="n">
         <v>216</v>
@@ -30246,7 +30246,7 @@
         <v>216</v>
       </c>
       <c r="R37" t="n">
-        <v>215.9999999999999</v>
+        <v>216</v>
       </c>
       <c r="S37" t="n">
         <v>216</v>
@@ -31097,7 +31097,7 @@
         <v>15.809608040201</v>
       </c>
       <c r="I2" t="n">
-        <v>59.51421105527639</v>
+        <v>59.51421105527641</v>
       </c>
       <c r="J2" t="n">
         <v>131.0211859296483</v>
@@ -31106,7 +31106,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L2" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="M2" t="n">
         <v>271.0634773869347</v>
@@ -31115,22 +31115,22 @@
         <v>275.449567839196</v>
       </c>
       <c r="O2" t="n">
-        <v>260.099216080402</v>
+        <v>260.0992160804021</v>
       </c>
       <c r="P2" t="n">
-        <v>221.9886633165829</v>
+        <v>221.988663316583</v>
       </c>
       <c r="Q2" t="n">
-        <v>166.7042412060301</v>
+        <v>166.7042412060302</v>
       </c>
       <c r="R2" t="n">
-        <v>96.97061306532665</v>
+        <v>96.97061306532667</v>
       </c>
       <c r="S2" t="n">
-        <v>35.17748743718594</v>
+        <v>35.17748743718595</v>
       </c>
       <c r="T2" t="n">
-        <v>6.757628140703516</v>
+        <v>6.757628140703518</v>
       </c>
       <c r="U2" t="n">
         <v>0.1234974874371858</v>
@@ -31170,31 +31170,31 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8259622641509434</v>
+        <v>0.8259622641509436</v>
       </c>
       <c r="H3" t="n">
-        <v>7.977056603773587</v>
+        <v>7.977056603773589</v>
       </c>
       <c r="I3" t="n">
-        <v>28.43773584905661</v>
+        <v>28.43773584905662</v>
       </c>
       <c r="J3" t="n">
-        <v>78.03532075471699</v>
+        <v>78.03532075471701</v>
       </c>
       <c r="K3" t="n">
         <v>133.3747924528302</v>
       </c>
       <c r="L3" t="n">
-        <v>179.3388679245283</v>
+        <v>179.3388679245284</v>
       </c>
       <c r="M3" t="n">
         <v>209.28</v>
       </c>
       <c r="N3" t="n">
-        <v>214.8190188679245</v>
+        <v>214.8190188679246</v>
       </c>
       <c r="O3" t="n">
-        <v>196.5174339622641</v>
+        <v>196.5174339622642</v>
       </c>
       <c r="P3" t="n">
         <v>157.7225660377359</v>
@@ -31203,16 +31203,16 @@
         <v>105.4333584905661</v>
       </c>
       <c r="R3" t="n">
-        <v>51.28211320754719</v>
+        <v>51.28211320754721</v>
       </c>
       <c r="S3" t="n">
         <v>15.34188679245282</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32920754716981</v>
+        <v>3.329207547169811</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05433962264150946</v>
+        <v>0.05433962264150947</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,19 +31249,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6924590163934425</v>
+        <v>0.6924590163934427</v>
       </c>
       <c r="H4" t="n">
-        <v>6.15659016393443</v>
+        <v>6.156590163934432</v>
       </c>
       <c r="I4" t="n">
         <v>20.82413114754099</v>
       </c>
       <c r="J4" t="n">
-        <v>48.95685245901639</v>
+        <v>48.9568524590164</v>
       </c>
       <c r="K4" t="n">
-        <v>80.45114754098358</v>
+        <v>80.4511475409836</v>
       </c>
       <c r="L4" t="n">
         <v>102.9497704918033</v>
@@ -31270,19 +31270,19 @@
         <v>108.5460983606557</v>
       </c>
       <c r="N4" t="n">
-        <v>105.9651147540984</v>
+        <v>105.9651147540985</v>
       </c>
       <c r="O4" t="n">
-        <v>97.87593442622953</v>
+        <v>97.87593442622956</v>
       </c>
       <c r="P4" t="n">
-        <v>83.74977049180323</v>
+        <v>83.74977049180325</v>
       </c>
       <c r="Q4" t="n">
-        <v>57.98399999999999</v>
+        <v>57.98400000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>31.13547540983605</v>
+        <v>31.13547540983606</v>
       </c>
       <c r="S4" t="n">
         <v>12.06767213114754</v>
@@ -31291,7 +31291,7 @@
         <v>2.958688524590163</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03777049180327872</v>
+        <v>0.03777049180327873</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31334,7 +31334,7 @@
         <v>15.809608040201</v>
       </c>
       <c r="I5" t="n">
-        <v>59.51421105527639</v>
+        <v>59.51421105527641</v>
       </c>
       <c r="J5" t="n">
         <v>131.0211859296483</v>
@@ -31343,7 +31343,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L5" t="n">
-        <v>223.0000000000002</v>
+        <v>223.0000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>271.0634773869347</v>
@@ -31352,22 +31352,22 @@
         <v>275.449567839196</v>
       </c>
       <c r="O5" t="n">
-        <v>260.099216080402</v>
+        <v>260.0992160804021</v>
       </c>
       <c r="P5" t="n">
-        <v>221.9886633165829</v>
+        <v>221.988663316583</v>
       </c>
       <c r="Q5" t="n">
-        <v>166.7042412060301</v>
+        <v>166.7042412060302</v>
       </c>
       <c r="R5" t="n">
-        <v>96.97061306532665</v>
+        <v>96.97061306532667</v>
       </c>
       <c r="S5" t="n">
-        <v>35.17748743718594</v>
+        <v>35.17748743718595</v>
       </c>
       <c r="T5" t="n">
-        <v>6.757628140703516</v>
+        <v>6.757628140703518</v>
       </c>
       <c r="U5" t="n">
         <v>0.1234974874371858</v>
@@ -31407,31 +31407,31 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8259622641509434</v>
+        <v>0.8259622641509436</v>
       </c>
       <c r="H6" t="n">
-        <v>7.977056603773587</v>
+        <v>7.977056603773589</v>
       </c>
       <c r="I6" t="n">
-        <v>28.43773584905661</v>
+        <v>28.43773584905662</v>
       </c>
       <c r="J6" t="n">
-        <v>78.03532075471699</v>
+        <v>78.03532075471701</v>
       </c>
       <c r="K6" t="n">
         <v>133.3747924528302</v>
       </c>
       <c r="L6" t="n">
-        <v>179.3388679245283</v>
+        <v>179.3388679245284</v>
       </c>
       <c r="M6" t="n">
         <v>209.28</v>
       </c>
       <c r="N6" t="n">
-        <v>214.8190188679245</v>
+        <v>214.8190188679246</v>
       </c>
       <c r="O6" t="n">
-        <v>196.5174339622641</v>
+        <v>196.5174339622642</v>
       </c>
       <c r="P6" t="n">
         <v>157.7225660377359</v>
@@ -31440,16 +31440,16 @@
         <v>105.4333584905661</v>
       </c>
       <c r="R6" t="n">
-        <v>51.28211320754719</v>
+        <v>51.28211320754721</v>
       </c>
       <c r="S6" t="n">
         <v>15.34188679245282</v>
       </c>
       <c r="T6" t="n">
-        <v>3.32920754716981</v>
+        <v>3.329207547169811</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05433962264150946</v>
+        <v>0.05433962264150947</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,19 +31486,19 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6924590163934425</v>
+        <v>0.6924590163934427</v>
       </c>
       <c r="H7" t="n">
-        <v>6.15659016393443</v>
+        <v>6.156590163934432</v>
       </c>
       <c r="I7" t="n">
         <v>20.82413114754099</v>
       </c>
       <c r="J7" t="n">
-        <v>48.95685245901639</v>
+        <v>48.9568524590164</v>
       </c>
       <c r="K7" t="n">
-        <v>80.45114754098358</v>
+        <v>80.4511475409836</v>
       </c>
       <c r="L7" t="n">
         <v>102.9497704918033</v>
@@ -31507,19 +31507,19 @@
         <v>108.5460983606557</v>
       </c>
       <c r="N7" t="n">
-        <v>105.9651147540984</v>
+        <v>105.9651147540985</v>
       </c>
       <c r="O7" t="n">
-        <v>97.87593442622953</v>
+        <v>97.87593442622956</v>
       </c>
       <c r="P7" t="n">
-        <v>83.74977049180323</v>
+        <v>83.74977049180325</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.98399999999999</v>
+        <v>57.98400000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>31.13547540983605</v>
+        <v>31.13547540983606</v>
       </c>
       <c r="S7" t="n">
         <v>12.06767213114754</v>
@@ -31528,7 +31528,7 @@
         <v>2.958688524590163</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03777049180327872</v>
+        <v>0.03777049180327873</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>15.809608040201</v>
       </c>
       <c r="I8" t="n">
-        <v>59.51421105527639</v>
+        <v>59.51421105527641</v>
       </c>
       <c r="J8" t="n">
         <v>131.0211859296483</v>
@@ -31580,7 +31580,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L8" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="M8" t="n">
         <v>271.0634773869347</v>
@@ -31589,22 +31589,22 @@
         <v>275.449567839196</v>
       </c>
       <c r="O8" t="n">
-        <v>260.099216080402</v>
+        <v>260.0992160804021</v>
       </c>
       <c r="P8" t="n">
-        <v>221.9886633165829</v>
+        <v>221.988663316583</v>
       </c>
       <c r="Q8" t="n">
-        <v>166.7042412060301</v>
+        <v>166.7042412060302</v>
       </c>
       <c r="R8" t="n">
-        <v>96.97061306532665</v>
+        <v>96.97061306532667</v>
       </c>
       <c r="S8" t="n">
-        <v>35.17748743718594</v>
+        <v>35.17748743718595</v>
       </c>
       <c r="T8" t="n">
-        <v>6.757628140703516</v>
+        <v>6.757628140703518</v>
       </c>
       <c r="U8" t="n">
         <v>0.1234974874371858</v>
@@ -31644,31 +31644,31 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8259622641509434</v>
+        <v>0.8259622641509436</v>
       </c>
       <c r="H9" t="n">
-        <v>7.977056603773587</v>
+        <v>7.977056603773589</v>
       </c>
       <c r="I9" t="n">
-        <v>28.43773584905661</v>
+        <v>28.43773584905662</v>
       </c>
       <c r="J9" t="n">
-        <v>78.03532075471699</v>
+        <v>78.03532075471701</v>
       </c>
       <c r="K9" t="n">
         <v>133.3747924528302</v>
       </c>
       <c r="L9" t="n">
-        <v>179.3388679245283</v>
+        <v>179.3388679245284</v>
       </c>
       <c r="M9" t="n">
         <v>209.28</v>
       </c>
       <c r="N9" t="n">
-        <v>214.8190188679245</v>
+        <v>214.8190188679246</v>
       </c>
       <c r="O9" t="n">
-        <v>196.5174339622641</v>
+        <v>196.5174339622642</v>
       </c>
       <c r="P9" t="n">
         <v>157.7225660377359</v>
@@ -31677,16 +31677,16 @@
         <v>105.4333584905661</v>
       </c>
       <c r="R9" t="n">
-        <v>51.28211320754719</v>
+        <v>51.28211320754721</v>
       </c>
       <c r="S9" t="n">
         <v>15.34188679245282</v>
       </c>
       <c r="T9" t="n">
-        <v>3.32920754716981</v>
+        <v>3.329207547169811</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05433962264150946</v>
+        <v>0.05433962264150947</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,19 +31723,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6924590163934425</v>
+        <v>0.6924590163934427</v>
       </c>
       <c r="H10" t="n">
-        <v>6.15659016393443</v>
+        <v>6.156590163934432</v>
       </c>
       <c r="I10" t="n">
         <v>20.82413114754099</v>
       </c>
       <c r="J10" t="n">
-        <v>48.95685245901639</v>
+        <v>48.9568524590164</v>
       </c>
       <c r="K10" t="n">
-        <v>80.45114754098358</v>
+        <v>80.4511475409836</v>
       </c>
       <c r="L10" t="n">
         <v>102.9497704918033</v>
@@ -31744,19 +31744,19 @@
         <v>108.5460983606557</v>
       </c>
       <c r="N10" t="n">
-        <v>105.9651147540984</v>
+        <v>105.9651147540985</v>
       </c>
       <c r="O10" t="n">
-        <v>97.87593442622953</v>
+        <v>97.87593442622956</v>
       </c>
       <c r="P10" t="n">
-        <v>83.74977049180323</v>
+        <v>83.74977049180325</v>
       </c>
       <c r="Q10" t="n">
-        <v>57.98399999999999</v>
+        <v>57.98400000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>31.13547540983605</v>
+        <v>31.13547540983606</v>
       </c>
       <c r="S10" t="n">
         <v>12.06767213114754</v>
@@ -31765,7 +31765,7 @@
         <v>2.958688524590163</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03777049180327872</v>
+        <v>0.03777049180327873</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L14" t="n">
-        <v>223.0000000000009</v>
+        <v>223.0000000000006</v>
       </c>
       <c r="M14" t="n">
         <v>271.0634773869347</v>
@@ -32291,7 +32291,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L17" t="n">
-        <v>223.0000000000008</v>
+        <v>223.0000000000005</v>
       </c>
       <c r="M17" t="n">
         <v>271.0634773869347</v>
@@ -32528,7 +32528,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L20" t="n">
-        <v>223.0000000000006</v>
+        <v>223.0000000000008</v>
       </c>
       <c r="M20" t="n">
         <v>271.0634773869347</v>
@@ -32765,7 +32765,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L23" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000009</v>
       </c>
       <c r="M23" t="n">
         <v>271.0634773869347</v>
@@ -33239,7 +33239,7 @@
         <v>189.0000000000002</v>
       </c>
       <c r="L29" t="n">
-        <v>189.0000000000002</v>
+        <v>189.0000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>271.0634773869347</v>
@@ -33473,10 +33473,10 @@
         <v>131.0211859296483</v>
       </c>
       <c r="K32" t="n">
-        <v>189.0000000000002</v>
+        <v>189.0000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>189.0000000000002</v>
+        <v>189.0000000000001</v>
       </c>
       <c r="M32" t="n">
         <v>271.0634773869347</v>
@@ -34199,7 +34199,7 @@
         <v>259.2478695740929</v>
       </c>
       <c r="P41" t="n">
-        <v>189.2870600406819</v>
+        <v>189.2870600406824</v>
       </c>
       <c r="Q41" t="n">
         <v>166.7042412060301</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>95.97817968455792</v>
+        <v>95.97817968455794</v>
       </c>
       <c r="K2" t="n">
         <v>196.3667939698493</v>
@@ -34761,7 +34761,7 @@
         <v>189.8513465063096</v>
       </c>
       <c r="P2" t="n">
-        <v>221.7016032759015</v>
+        <v>221.7016032759016</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34825,22 +34825,22 @@
         <v>203.2439269923927</v>
       </c>
       <c r="K3" t="n">
-        <v>28.59840623060801</v>
+        <v>28.59840623060803</v>
       </c>
       <c r="L3" t="n">
-        <v>65.34090681341722</v>
+        <v>65.34090681341725</v>
       </c>
       <c r="M3" t="n">
-        <v>84.51400188937596</v>
+        <v>84.51400188937534</v>
       </c>
       <c r="N3" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000002</v>
       </c>
       <c r="O3" t="n">
-        <v>55.29265706410681</v>
+        <v>55.29265706410686</v>
       </c>
       <c r="P3" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000002</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34901,7 +34901,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>13.68790362310862</v>
+        <v>13.68790362310864</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34980,13 +34980,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>95.97817968455792</v>
+        <v>95.97817968455794</v>
       </c>
       <c r="K5" t="n">
         <v>196.3667939698493</v>
       </c>
       <c r="L5" t="n">
-        <v>223.0000000000002</v>
+        <v>223.0000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -34998,7 +34998,7 @@
         <v>189.8513465063096</v>
       </c>
       <c r="P5" t="n">
-        <v>221.7016032759015</v>
+        <v>221.7016032759016</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -35062,22 +35062,22 @@
         <v>203.2439269923927</v>
       </c>
       <c r="K6" t="n">
-        <v>223.0000000000004</v>
+        <v>28.59840623060803</v>
       </c>
       <c r="L6" t="n">
-        <v>65.34090681341722</v>
+        <v>65.34090681341725</v>
       </c>
       <c r="M6" t="n">
-        <v>223.0000000000004</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>60.87454940814443</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="O6" t="n">
-        <v>55.29265706410681</v>
+        <v>139.8066589534826</v>
       </c>
       <c r="P6" t="n">
-        <v>52.23785871183962</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35138,7 +35138,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>13.68790362310862</v>
+        <v>13.68790362310864</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>95.97817968455792</v>
+        <v>95.97817968455794</v>
       </c>
       <c r="K8" t="n">
         <v>196.3667939698493</v>
       </c>
       <c r="L8" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000003</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35235,7 +35235,7 @@
         <v>189.8513465063096</v>
       </c>
       <c r="P8" t="n">
-        <v>221.7016032759015</v>
+        <v>221.7016032759016</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35299,22 +35299,22 @@
         <v>203.2439269923927</v>
       </c>
       <c r="K9" t="n">
-        <v>60.87454940814455</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="L9" t="n">
-        <v>65.34090681341722</v>
+        <v>65.34090681341725</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>113.112408119984</v>
+      </c>
+      <c r="O9" t="n">
+        <v>55.29265706410686</v>
+      </c>
+      <c r="P9" t="n">
         <v>223.0000000000004</v>
-      </c>
-      <c r="N9" t="n">
-        <v>223.0000000000004</v>
-      </c>
-      <c r="O9" t="n">
-        <v>55.29265706410681</v>
-      </c>
-      <c r="P9" t="n">
-        <v>52.23785871183962</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35375,7 +35375,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>13.68790362310862</v>
+        <v>13.68790362310864</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35460,7 +35460,7 @@
         <v>196.3667939698493</v>
       </c>
       <c r="L11" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35533,25 +35533,25 @@
         <v>37.31134995770807</v>
       </c>
       <c r="J12" t="n">
-        <v>201.7791850646043</v>
+        <v>7.001244745033062</v>
       </c>
       <c r="K12" t="n">
         <v>28.59840623060801</v>
       </c>
       <c r="L12" t="n">
-        <v>72.43320742215538</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="M12" t="n">
-        <v>50.53522173439683</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>90.03704180522911</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>208.9787300068095</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="P12" t="n">
-        <v>52.23785871183962</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="Q12" t="n">
         <v>141.0788980565531</v>
@@ -35697,7 +35697,7 @@
         <v>196.3667939698492</v>
       </c>
       <c r="L14" t="n">
-        <v>223.0000000000009</v>
+        <v>223.0000000000006</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -35770,13 +35770,13 @@
         <v>19.583768065179</v>
       </c>
       <c r="J15" t="n">
-        <v>215.1125564227623</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>28.59840623060801</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="L15" t="n">
-        <v>65.34090681341722</v>
+        <v>83.51711061670497</v>
       </c>
       <c r="M15" t="n">
         <v>50.53522173439683</v>
@@ -35785,7 +35785,7 @@
         <v>90.03704180522911</v>
       </c>
       <c r="O15" t="n">
-        <v>220.4652411499166</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="P15" t="n">
         <v>52.23785871183962</v>
@@ -35931,10 +35931,10 @@
         <v>95.97817968455792</v>
       </c>
       <c r="K17" t="n">
-        <v>196.3667939698492</v>
+        <v>196.3667939698493</v>
       </c>
       <c r="L17" t="n">
-        <v>223.0000000000008</v>
+        <v>223.0000000000005</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -36007,22 +36007,22 @@
         <v>19.583768065179</v>
       </c>
       <c r="J18" t="n">
-        <v>201.7791850646043</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>28.59840623060801</v>
       </c>
       <c r="L18" t="n">
-        <v>148.90136578319</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="M18" t="n">
-        <v>50.53522173439683</v>
+        <v>88.17873077695857</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>90.03704180522911</v>
       </c>
       <c r="O18" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="P18" t="n">
         <v>52.23785871183962</v>
@@ -36086,7 +36086,7 @@
         <v>70.19067552742271</v>
       </c>
       <c r="J19" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000004</v>
       </c>
       <c r="K19" t="n">
         <v>17.93037373984055</v>
@@ -36168,10 +36168,10 @@
         <v>95.97817968455792</v>
       </c>
       <c r="K20" t="n">
-        <v>196.3667939698493</v>
+        <v>196.3667939698492</v>
       </c>
       <c r="L20" t="n">
-        <v>223.0000000000005</v>
+        <v>223.0000000000008</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -36244,13 +36244,13 @@
         <v>19.583768065179</v>
       </c>
       <c r="J21" t="n">
-        <v>201.7791850646043</v>
+        <v>223.0000000000005</v>
       </c>
       <c r="K21" t="n">
         <v>28.59840623060801</v>
       </c>
       <c r="L21" t="n">
-        <v>217.2184173780446</v>
+        <v>65.34090681341722</v>
       </c>
       <c r="M21" t="n">
         <v>50.53522173439683</v>
@@ -36259,13 +36259,13 @@
         <v>90.03704180522911</v>
       </c>
       <c r="O21" t="n">
-        <v>223.0000000000005</v>
+        <v>55.29265706410681</v>
       </c>
       <c r="P21" t="n">
-        <v>52.23785871183962</v>
+        <v>209.5229992204117</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>141.0788980565531</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36408,7 +36408,7 @@
         <v>196.3667939698492</v>
       </c>
       <c r="L23" t="n">
-        <v>223.0000000000003</v>
+        <v>223.0000000000009</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36487,7 +36487,7 @@
         <v>28.59840623060801</v>
       </c>
       <c r="L24" t="n">
-        <v>76.139519321492</v>
+        <v>76.13951932149195</v>
       </c>
       <c r="M24" t="n">
         <v>50.53522173439683</v>
@@ -36718,19 +36718,19 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>67.20814904213807</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>28.59840623060801</v>
       </c>
       <c r="L27" t="n">
-        <v>65.34090681341722</v>
+        <v>189</v>
       </c>
       <c r="M27" t="n">
         <v>28.53522173439683</v>
       </c>
       <c r="N27" t="n">
-        <v>68.03704180522911</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>55.29265706410681</v>
@@ -36739,7 +36739,7 @@
         <v>52.23785871183962</v>
       </c>
       <c r="Q27" t="n">
-        <v>119.0788980565531</v>
+        <v>116.0361064798371</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36794,7 +36794,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>25.84437098625069</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
         <v>189.0000000000003</v>
       </c>
       <c r="L29" t="n">
-        <v>189.0000000000002</v>
+        <v>189.0000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>9.583768065179001</v>
+        <v>27.31134995770807</v>
       </c>
       <c r="J30" t="n">
         <v>189.0000000000001</v>
@@ -36964,19 +36964,19 @@
         <v>65.34090681341722</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>40.53522173439683</v>
       </c>
       <c r="N30" t="n">
         <v>80.03704180522911</v>
       </c>
       <c r="O30" t="n">
-        <v>55.29265706410681</v>
+        <v>116.9487577103527</v>
       </c>
       <c r="P30" t="n">
-        <v>189.0000000000001</v>
+        <v>52.23785871183962</v>
       </c>
       <c r="Q30" t="n">
-        <v>131.5108563850977</v>
+        <v>148.3540934000865</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,10 +37116,10 @@
         <v>95.97817968455792</v>
       </c>
       <c r="K32" t="n">
-        <v>189.0000000000002</v>
+        <v>189.0000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>189.0000000000002</v>
+        <v>189.0000000000001</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -37192,10 +37192,10 @@
         <v>9.583768065179001</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>189.0000000000003</v>
       </c>
       <c r="K33" t="n">
-        <v>125.8043699326206</v>
+        <v>125.2572841129166</v>
       </c>
       <c r="L33" t="n">
         <v>65.34090681341722</v>
@@ -37207,13 +37207,13 @@
         <v>80.03704180522911</v>
       </c>
       <c r="O33" t="n">
-        <v>89.70823461270908</v>
+        <v>55.29265706410681</v>
       </c>
       <c r="P33" t="n">
-        <v>189.0000000000003</v>
+        <v>52.23785871183962</v>
       </c>
       <c r="Q33" t="n">
-        <v>148.3540934000865</v>
+        <v>131.0788980565531</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37429,13 +37429,13 @@
         <v>9.583768065179001</v>
       </c>
       <c r="J36" t="n">
-        <v>189.0000000000004</v>
+        <v>124.1511355909352</v>
       </c>
       <c r="K36" t="n">
         <v>28.59840623060801</v>
       </c>
       <c r="L36" t="n">
-        <v>161.9997846957264</v>
+        <v>65.34090681341722</v>
       </c>
       <c r="M36" t="n">
         <v>40.53522173439683</v>
@@ -37444,10 +37444,10 @@
         <v>80.03704180522911</v>
       </c>
       <c r="O36" t="n">
-        <v>55.29265706410681</v>
+        <v>80.03825806732031</v>
       </c>
       <c r="P36" t="n">
-        <v>52.23785871183962</v>
+        <v>189.0000000000004</v>
       </c>
       <c r="Q36" t="n">
         <v>131.0788980565531</v>
